--- a/vorlagen/Kostenstellen_BWA_Vorlage.xlsx
+++ b/vorlagen/Kostenstellen_BWA_Vorlage.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Alle Objekte" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="KSt 1" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="KSt 2" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alle Objekte" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KSt 1" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KSt 2" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3171,7 +3171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:AN50"/>
+  <dimension ref="B2:AN61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="3" max="3"/>
@@ -5781,6 +5781,71 @@
       <c r="AM50" s="4" t="n"/>
       <c r="AN50" s="4" t="n"/>
     </row>
+    <row r="53">
+      <c r="C53" s="1" t="inlineStr">
+        <is>
+          <t>Buchwert, JE</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>496000</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Wohnbau 1</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>496000</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="C56" s="1" t="inlineStr">
+        <is>
+          <t>Abschreibungen JW</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>16000</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="G57" t="n">
+        <v>16000</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Wohnbau 1</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>16000</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="C60" s="1" t="inlineStr">
+        <is>
+          <t>Abschreibungen MW</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>1333.333333333333</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Wohnbau 1</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>1333.33</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5792,7 +5857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:AN50"/>
+  <dimension ref="B2:AN70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="3" max="3"/>
@@ -8522,6 +8587,158 @@
       <c r="AM50" s="4" t="n"/>
       <c r="AN50" s="4" t="n"/>
     </row>
+    <row r="53">
+      <c r="C53" s="1" t="inlineStr">
+        <is>
+          <t>Buchwert, JE</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>941000</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Wohnbau 7</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>876000</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Außenanlagen 7</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Anbau im Bau</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>sonstige</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="C59" s="1" t="inlineStr">
+        <is>
+          <t>Abschreibungen JW</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="G60" t="n">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Wohnbau</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>24000</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Außenanlagen</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Anbau im Bau</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>sonstige</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="C66" s="1" t="inlineStr">
+        <is>
+          <t>Abschreibungen MW</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Wohnbau</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Außenanlagen</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Anbau im Bau</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>sonstige</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vorlagen/Kostenstellen_BWA_Vorlage.xlsx
+++ b/vorlagen/Kostenstellen_BWA_Vorlage.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:AN50"/>
+  <dimension ref="B2:AN51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="3" max="3"/>
@@ -1582,11 +1582,11 @@
     </row>
     <row r="23">
       <c r="B23" t="n">
-        <v>1180</v>
+        <v>1160</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Kfz-Kosten (o. St.)</t>
+          <t>Besondere Kosten</t>
         </is>
       </c>
       <c r="F23" s="4" t="n"/>
@@ -1627,11 +1627,11 @@
     </row>
     <row r="24">
       <c r="B24" t="n">
-        <v>1200</v>
+        <v>1180</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Werbe-/Reisekosten</t>
+          <t>Kfz-Kosten (o. St.)</t>
         </is>
       </c>
       <c r="F24" s="4" t="n"/>
@@ -1672,11 +1672,11 @@
     </row>
     <row r="25">
       <c r="B25" t="n">
-        <v>1220</v>
+        <v>1200</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Kosten Warenabgabe</t>
+          <t>Werbe-/Reisekosten</t>
         </is>
       </c>
       <c r="F25" s="4" t="n"/>
@@ -1717,58 +1717,28 @@
     </row>
     <row r="26">
       <c r="B26" t="n">
-        <v>1240</v>
+        <v>1220</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Abschreibungen</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="n">
-        <v>44160</v>
-      </c>
-      <c r="G26" s="4" t="n">
-        <v>45080</v>
-      </c>
-      <c r="H26" s="4" t="n">
-        <v>3833.33</v>
-      </c>
-      <c r="I26" s="4" t="n">
-        <v>3833.33</v>
-      </c>
-      <c r="J26" s="4" t="n">
-        <v>3833.33</v>
-      </c>
-      <c r="K26" s="4" t="n">
-        <v>3833.33</v>
-      </c>
-      <c r="L26" s="4" t="n">
-        <v>3833.33</v>
-      </c>
-      <c r="M26" s="4" t="n">
-        <v>3833.33</v>
-      </c>
-      <c r="N26" s="4" t="n">
-        <v>3833.33</v>
-      </c>
-      <c r="O26" s="4" t="n">
-        <v>3833.33</v>
-      </c>
-      <c r="P26" s="4" t="n">
-        <v>3833.33</v>
-      </c>
-      <c r="Q26" s="4" t="n">
-        <v>3833.33</v>
-      </c>
-      <c r="R26" s="4" t="n">
-        <v>3833.33</v>
-      </c>
-      <c r="S26" s="4" t="n">
-        <v>3833.33</v>
-      </c>
-      <c r="T26" s="4" t="n">
-        <v>46000</v>
-      </c>
+          <t>Kosten Warenabgabe</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="n"/>
+      <c r="G26" s="4" t="n"/>
+      <c r="H26" s="4" t="n"/>
+      <c r="I26" s="4" t="n"/>
+      <c r="J26" s="4" t="n"/>
+      <c r="K26" s="4" t="n"/>
+      <c r="L26" s="4" t="n"/>
+      <c r="M26" s="4" t="n"/>
+      <c r="N26" s="4" t="n"/>
+      <c r="O26" s="4" t="n"/>
+      <c r="P26" s="4" t="n"/>
+      <c r="Q26" s="4" t="n"/>
+      <c r="R26" s="4" t="n"/>
+      <c r="S26" s="4" t="n"/>
+      <c r="T26" s="4" t="n"/>
       <c r="U26" s="4" t="n"/>
       <c r="V26" s="4" t="n"/>
       <c r="W26" s="4" t="n"/>
@@ -1792,57 +1762,57 @@
     </row>
     <row r="27">
       <c r="B27" t="n">
-        <v>1250</v>
+        <v>1240</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Reparatur/Instandh.</t>
+          <t>Abschreibungen</t>
         </is>
       </c>
       <c r="F27" s="4" t="n">
-        <v>21120</v>
+        <v>44160</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>21560</v>
+        <v>45080</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>1833.33</v>
+        <v>3833.33</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>1833.33</v>
+        <v>3833.33</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>1833.33</v>
+        <v>3833.33</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>1833.33</v>
+        <v>3833.33</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>1833.33</v>
+        <v>3833.33</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>1833.33</v>
+        <v>3833.33</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>1833.33</v>
+        <v>3833.33</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>1833.33</v>
+        <v>3833.33</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>1833.33</v>
+        <v>3833.33</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>1833.33</v>
+        <v>3833.33</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>1833.33</v>
+        <v>3833.33</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>1833.33</v>
+        <v>3833.33</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>22000</v>
+        <v>46000</v>
       </c>
       <c r="U27" s="4" t="n"/>
       <c r="V27" s="4" t="n"/>
@@ -1867,57 +1837,57 @@
     </row>
     <row r="28">
       <c r="B28" t="n">
-        <v>1260</v>
+        <v>1250</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sonstige Kosten</t>
+          <t>Reparatur/Instandh.</t>
         </is>
       </c>
       <c r="F28" s="4" t="n">
-        <v>1632</v>
+        <v>21120</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>1666</v>
+        <v>21560</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>141.67</v>
+        <v>1833.33</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>141.67</v>
+        <v>1833.33</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>141.67</v>
+        <v>1833.33</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>141.67</v>
+        <v>1833.33</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>141.67</v>
+        <v>1833.33</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>141.67</v>
+        <v>1833.33</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>141.67</v>
+        <v>1833.33</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>141.67</v>
+        <v>1833.33</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>141.67</v>
+        <v>1833.33</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>141.67</v>
+        <v>1833.33</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>141.67</v>
+        <v>1833.33</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>141.67</v>
+        <v>1833.33</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>1700</v>
+        <v>22000</v>
       </c>
       <c r="U28" s="4" t="n"/>
       <c r="V28" s="4" t="n"/>
@@ -1942,57 +1912,57 @@
     </row>
     <row r="29">
       <c r="B29" t="n">
-        <v>1280</v>
+        <v>1260</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Gesamtkosten</t>
+          <t>Sonstige Kosten</t>
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>77664</v>
+        <v>1632</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>79282</v>
+        <v>1666</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>6741.67</v>
+        <v>141.67</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>6741.67</v>
+        <v>141.67</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>6741.67</v>
+        <v>141.67</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>6741.67</v>
+        <v>141.67</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>6741.67</v>
+        <v>141.67</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>6741.67</v>
+        <v>141.67</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>6741.67</v>
+        <v>141.67</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>6741.67</v>
+        <v>141.67</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>6741.67</v>
+        <v>141.67</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>6741.67</v>
+        <v>141.67</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>6741.67</v>
+        <v>141.67</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>6741.67</v>
+        <v>141.67</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>80900</v>
+        <v>1700</v>
       </c>
       <c r="U29" s="4" t="n"/>
       <c r="V29" s="4" t="n"/>
@@ -2017,23 +1987,58 @@
     </row>
     <row r="30">
       <c r="B30" t="n">
-        <v>1290</v>
-      </c>
-      <c r="F30" s="4" t="n"/>
-      <c r="G30" s="4" t="n"/>
-      <c r="H30" s="4" t="n"/>
-      <c r="I30" s="4" t="n"/>
-      <c r="J30" s="4" t="n"/>
-      <c r="K30" s="4" t="n"/>
-      <c r="L30" s="4" t="n"/>
-      <c r="M30" s="4" t="n"/>
-      <c r="N30" s="4" t="n"/>
-      <c r="O30" s="4" t="n"/>
-      <c r="P30" s="4" t="n"/>
-      <c r="Q30" s="4" t="n"/>
-      <c r="R30" s="4" t="n"/>
-      <c r="S30" s="4" t="n"/>
-      <c r="T30" s="4" t="n"/>
+        <v>1280</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Gesamtkosten</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>77664</v>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>79282</v>
+      </c>
+      <c r="H30" s="4" t="n">
+        <v>6741.67</v>
+      </c>
+      <c r="I30" s="4" t="n">
+        <v>6741.67</v>
+      </c>
+      <c r="J30" s="4" t="n">
+        <v>6741.67</v>
+      </c>
+      <c r="K30" s="4" t="n">
+        <v>6741.67</v>
+      </c>
+      <c r="L30" s="4" t="n">
+        <v>6741.67</v>
+      </c>
+      <c r="M30" s="4" t="n">
+        <v>6741.67</v>
+      </c>
+      <c r="N30" s="4" t="n">
+        <v>6741.67</v>
+      </c>
+      <c r="O30" s="4" t="n">
+        <v>6741.67</v>
+      </c>
+      <c r="P30" s="4" t="n">
+        <v>6741.67</v>
+      </c>
+      <c r="Q30" s="4" t="n">
+        <v>6741.67</v>
+      </c>
+      <c r="R30" s="4" t="n">
+        <v>6741.67</v>
+      </c>
+      <c r="S30" s="4" t="n">
+        <v>6741.67</v>
+      </c>
+      <c r="T30" s="4" t="n">
+        <v>80900</v>
+      </c>
       <c r="U30" s="4" t="n"/>
       <c r="V30" s="4" t="n"/>
       <c r="W30" s="4" t="n"/>
@@ -2057,58 +2062,23 @@
     </row>
     <row r="31">
       <c r="B31" t="n">
-        <v>1300</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Betriebsergebnis</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="n">
-        <v>96576</v>
-      </c>
-      <c r="G31" s="4" t="n">
-        <v>98588</v>
-      </c>
-      <c r="H31" s="4" t="n">
-        <v>8383.33</v>
-      </c>
-      <c r="I31" s="4" t="n">
-        <v>8383.33</v>
-      </c>
-      <c r="J31" s="4" t="n">
-        <v>8383.33</v>
-      </c>
-      <c r="K31" s="4" t="n">
-        <v>8383.33</v>
-      </c>
-      <c r="L31" s="4" t="n">
-        <v>8383.33</v>
-      </c>
-      <c r="M31" s="4" t="n">
-        <v>8383.33</v>
-      </c>
-      <c r="N31" s="4" t="n">
-        <v>8383.33</v>
-      </c>
-      <c r="O31" s="4" t="n">
-        <v>8383.33</v>
-      </c>
-      <c r="P31" s="4" t="n">
-        <v>8383.33</v>
-      </c>
-      <c r="Q31" s="4" t="n">
-        <v>8383.33</v>
-      </c>
-      <c r="R31" s="4" t="n">
-        <v>8383.33</v>
-      </c>
-      <c r="S31" s="4" t="n">
-        <v>8383.33</v>
-      </c>
-      <c r="T31" s="4" t="n">
-        <v>100600</v>
-      </c>
+        <v>1290</v>
+      </c>
+      <c r="F31" s="4" t="n"/>
+      <c r="G31" s="4" t="n"/>
+      <c r="H31" s="4" t="n"/>
+      <c r="I31" s="4" t="n"/>
+      <c r="J31" s="4" t="n"/>
+      <c r="K31" s="4" t="n"/>
+      <c r="L31" s="4" t="n"/>
+      <c r="M31" s="4" t="n"/>
+      <c r="N31" s="4" t="n"/>
+      <c r="O31" s="4" t="n"/>
+      <c r="P31" s="4" t="n"/>
+      <c r="Q31" s="4" t="n"/>
+      <c r="R31" s="4" t="n"/>
+      <c r="S31" s="4" t="n"/>
+      <c r="T31" s="4" t="n"/>
       <c r="U31" s="4" t="n"/>
       <c r="V31" s="4" t="n"/>
       <c r="W31" s="4" t="n"/>
@@ -2132,23 +2102,58 @@
     </row>
     <row r="32">
       <c r="B32" t="n">
-        <v>1301</v>
-      </c>
-      <c r="F32" s="4" t="n"/>
-      <c r="G32" s="4" t="n"/>
-      <c r="H32" s="4" t="n"/>
-      <c r="I32" s="4" t="n"/>
-      <c r="J32" s="4" t="n"/>
-      <c r="K32" s="4" t="n"/>
-      <c r="L32" s="4" t="n"/>
-      <c r="M32" s="4" t="n"/>
-      <c r="N32" s="4" t="n"/>
-      <c r="O32" s="4" t="n"/>
-      <c r="P32" s="4" t="n"/>
-      <c r="Q32" s="4" t="n"/>
-      <c r="R32" s="4" t="n"/>
-      <c r="S32" s="4" t="n"/>
-      <c r="T32" s="4" t="n"/>
+        <v>1300</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Betriebsergebnis</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>96576</v>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>98588</v>
+      </c>
+      <c r="H32" s="4" t="n">
+        <v>8383.33</v>
+      </c>
+      <c r="I32" s="4" t="n">
+        <v>8383.33</v>
+      </c>
+      <c r="J32" s="4" t="n">
+        <v>8383.33</v>
+      </c>
+      <c r="K32" s="4" t="n">
+        <v>8383.33</v>
+      </c>
+      <c r="L32" s="4" t="n">
+        <v>8383.33</v>
+      </c>
+      <c r="M32" s="4" t="n">
+        <v>8383.33</v>
+      </c>
+      <c r="N32" s="4" t="n">
+        <v>8383.33</v>
+      </c>
+      <c r="O32" s="4" t="n">
+        <v>8383.33</v>
+      </c>
+      <c r="P32" s="4" t="n">
+        <v>8383.33</v>
+      </c>
+      <c r="Q32" s="4" t="n">
+        <v>8383.33</v>
+      </c>
+      <c r="R32" s="4" t="n">
+        <v>8383.33</v>
+      </c>
+      <c r="S32" s="4" t="n">
+        <v>8383.33</v>
+      </c>
+      <c r="T32" s="4" t="n">
+        <v>100600</v>
+      </c>
       <c r="U32" s="4" t="n"/>
       <c r="V32" s="4" t="n"/>
       <c r="W32" s="4" t="n"/>
@@ -2172,58 +2177,23 @@
     </row>
     <row r="33">
       <c r="B33" t="n">
-        <v>1310</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Zinsaufwand</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="n">
-        <v>12480</v>
-      </c>
-      <c r="G33" s="4" t="n">
-        <v>12740</v>
-      </c>
-      <c r="H33" s="4" t="n">
-        <v>1083.33</v>
-      </c>
-      <c r="I33" s="4" t="n">
-        <v>1083.33</v>
-      </c>
-      <c r="J33" s="4" t="n">
-        <v>1083.33</v>
-      </c>
-      <c r="K33" s="4" t="n">
-        <v>1083.33</v>
-      </c>
-      <c r="L33" s="4" t="n">
-        <v>1083.33</v>
-      </c>
-      <c r="M33" s="4" t="n">
-        <v>1083.33</v>
-      </c>
-      <c r="N33" s="4" t="n">
-        <v>1083.33</v>
-      </c>
-      <c r="O33" s="4" t="n">
-        <v>1083.33</v>
-      </c>
-      <c r="P33" s="4" t="n">
-        <v>1083.33</v>
-      </c>
-      <c r="Q33" s="4" t="n">
-        <v>1083.33</v>
-      </c>
-      <c r="R33" s="4" t="n">
-        <v>1083.33</v>
-      </c>
-      <c r="S33" s="4" t="n">
-        <v>1083.33</v>
-      </c>
-      <c r="T33" s="4" t="n">
-        <v>13000</v>
-      </c>
+        <v>1301</v>
+      </c>
+      <c r="F33" s="4" t="n"/>
+      <c r="G33" s="4" t="n"/>
+      <c r="H33" s="4" t="n"/>
+      <c r="I33" s="4" t="n"/>
+      <c r="J33" s="4" t="n"/>
+      <c r="K33" s="4" t="n"/>
+      <c r="L33" s="4" t="n"/>
+      <c r="M33" s="4" t="n"/>
+      <c r="N33" s="4" t="n"/>
+      <c r="O33" s="4" t="n"/>
+      <c r="P33" s="4" t="n"/>
+      <c r="Q33" s="4" t="n"/>
+      <c r="R33" s="4" t="n"/>
+      <c r="S33" s="4" t="n"/>
+      <c r="T33" s="4" t="n"/>
       <c r="U33" s="4" t="n"/>
       <c r="V33" s="4" t="n"/>
       <c r="W33" s="4" t="n"/>
@@ -2247,28 +2217,58 @@
     </row>
     <row r="34">
       <c r="B34" t="n">
-        <v>1312</v>
+        <v>1310</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sonst. neutr. Aufw</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="n"/>
-      <c r="G34" s="4" t="n"/>
-      <c r="H34" s="4" t="n"/>
-      <c r="I34" s="4" t="n"/>
-      <c r="J34" s="4" t="n"/>
-      <c r="K34" s="4" t="n"/>
-      <c r="L34" s="4" t="n"/>
-      <c r="M34" s="4" t="n"/>
-      <c r="N34" s="4" t="n"/>
-      <c r="O34" s="4" t="n"/>
-      <c r="P34" s="4" t="n"/>
-      <c r="Q34" s="4" t="n"/>
-      <c r="R34" s="4" t="n"/>
-      <c r="S34" s="4" t="n"/>
-      <c r="T34" s="4" t="n"/>
+          <t>Zinsaufwand</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>12480</v>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>12740</v>
+      </c>
+      <c r="H34" s="4" t="n">
+        <v>1083.33</v>
+      </c>
+      <c r="I34" s="4" t="n">
+        <v>1083.33</v>
+      </c>
+      <c r="J34" s="4" t="n">
+        <v>1083.33</v>
+      </c>
+      <c r="K34" s="4" t="n">
+        <v>1083.33</v>
+      </c>
+      <c r="L34" s="4" t="n">
+        <v>1083.33</v>
+      </c>
+      <c r="M34" s="4" t="n">
+        <v>1083.33</v>
+      </c>
+      <c r="N34" s="4" t="n">
+        <v>1083.33</v>
+      </c>
+      <c r="O34" s="4" t="n">
+        <v>1083.33</v>
+      </c>
+      <c r="P34" s="4" t="n">
+        <v>1083.33</v>
+      </c>
+      <c r="Q34" s="4" t="n">
+        <v>1083.33</v>
+      </c>
+      <c r="R34" s="4" t="n">
+        <v>1083.33</v>
+      </c>
+      <c r="S34" s="4" t="n">
+        <v>1083.33</v>
+      </c>
+      <c r="T34" s="4" t="n">
+        <v>13000</v>
+      </c>
       <c r="U34" s="4" t="n"/>
       <c r="V34" s="4" t="n"/>
       <c r="W34" s="4" t="n"/>
@@ -2292,58 +2292,28 @@
     </row>
     <row r="35">
       <c r="B35" t="n">
-        <v>1320</v>
+        <v>1312</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Neutraler Aufwand</t>
-        </is>
-      </c>
-      <c r="F35" s="4" t="n">
-        <v>12480</v>
-      </c>
-      <c r="G35" s="4" t="n">
-        <v>12740</v>
-      </c>
-      <c r="H35" s="4" t="n">
-        <v>1083.33</v>
-      </c>
-      <c r="I35" s="4" t="n">
-        <v>1083.33</v>
-      </c>
-      <c r="J35" s="4" t="n">
-        <v>1083.33</v>
-      </c>
-      <c r="K35" s="4" t="n">
-        <v>1083.33</v>
-      </c>
-      <c r="L35" s="4" t="n">
-        <v>1083.33</v>
-      </c>
-      <c r="M35" s="4" t="n">
-        <v>1083.33</v>
-      </c>
-      <c r="N35" s="4" t="n">
-        <v>1083.33</v>
-      </c>
-      <c r="O35" s="4" t="n">
-        <v>1083.33</v>
-      </c>
-      <c r="P35" s="4" t="n">
-        <v>1083.33</v>
-      </c>
-      <c r="Q35" s="4" t="n">
-        <v>1083.33</v>
-      </c>
-      <c r="R35" s="4" t="n">
-        <v>1083.33</v>
-      </c>
-      <c r="S35" s="4" t="n">
-        <v>1083.33</v>
-      </c>
-      <c r="T35" s="4" t="n">
-        <v>13000</v>
-      </c>
+          <t>Sonst. neutr. Aufw</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="n"/>
+      <c r="G35" s="4" t="n"/>
+      <c r="H35" s="4" t="n"/>
+      <c r="I35" s="4" t="n"/>
+      <c r="J35" s="4" t="n"/>
+      <c r="K35" s="4" t="n"/>
+      <c r="L35" s="4" t="n"/>
+      <c r="M35" s="4" t="n"/>
+      <c r="N35" s="4" t="n"/>
+      <c r="O35" s="4" t="n"/>
+      <c r="P35" s="4" t="n"/>
+      <c r="Q35" s="4" t="n"/>
+      <c r="R35" s="4" t="n"/>
+      <c r="S35" s="4" t="n"/>
+      <c r="T35" s="4" t="n"/>
       <c r="U35" s="4" t="n"/>
       <c r="V35" s="4" t="n"/>
       <c r="W35" s="4" t="n"/>
@@ -2367,23 +2337,58 @@
     </row>
     <row r="36">
       <c r="B36" t="n">
-        <v>1321</v>
-      </c>
-      <c r="F36" s="4" t="n"/>
-      <c r="G36" s="4" t="n"/>
-      <c r="H36" s="4" t="n"/>
-      <c r="I36" s="4" t="n"/>
-      <c r="J36" s="4" t="n"/>
-      <c r="K36" s="4" t="n"/>
-      <c r="L36" s="4" t="n"/>
-      <c r="M36" s="4" t="n"/>
-      <c r="N36" s="4" t="n"/>
-      <c r="O36" s="4" t="n"/>
-      <c r="P36" s="4" t="n"/>
-      <c r="Q36" s="4" t="n"/>
-      <c r="R36" s="4" t="n"/>
-      <c r="S36" s="4" t="n"/>
-      <c r="T36" s="4" t="n"/>
+        <v>1320</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Neutraler Aufwand</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>12480</v>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>12740</v>
+      </c>
+      <c r="H36" s="4" t="n">
+        <v>1083.33</v>
+      </c>
+      <c r="I36" s="4" t="n">
+        <v>1083.33</v>
+      </c>
+      <c r="J36" s="4" t="n">
+        <v>1083.33</v>
+      </c>
+      <c r="K36" s="4" t="n">
+        <v>1083.33</v>
+      </c>
+      <c r="L36" s="4" t="n">
+        <v>1083.33</v>
+      </c>
+      <c r="M36" s="4" t="n">
+        <v>1083.33</v>
+      </c>
+      <c r="N36" s="4" t="n">
+        <v>1083.33</v>
+      </c>
+      <c r="O36" s="4" t="n">
+        <v>1083.33</v>
+      </c>
+      <c r="P36" s="4" t="n">
+        <v>1083.33</v>
+      </c>
+      <c r="Q36" s="4" t="n">
+        <v>1083.33</v>
+      </c>
+      <c r="R36" s="4" t="n">
+        <v>1083.33</v>
+      </c>
+      <c r="S36" s="4" t="n">
+        <v>1083.33</v>
+      </c>
+      <c r="T36" s="4" t="n">
+        <v>13000</v>
+      </c>
       <c r="U36" s="4" t="n"/>
       <c r="V36" s="4" t="n"/>
       <c r="W36" s="4" t="n"/>
@@ -2407,58 +2412,23 @@
     </row>
     <row r="37">
       <c r="B37" t="n">
-        <v>1322</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Zinserträge</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="n">
-        <v>288</v>
-      </c>
-      <c r="G37" s="4" t="n">
-        <v>294</v>
-      </c>
-      <c r="H37" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="I37" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="J37" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="K37" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="L37" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="M37" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="N37" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="O37" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="P37" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q37" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="R37" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="S37" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="T37" s="4" t="n">
-        <v>300</v>
-      </c>
+        <v>1321</v>
+      </c>
+      <c r="F37" s="4" t="n"/>
+      <c r="G37" s="4" t="n"/>
+      <c r="H37" s="4" t="n"/>
+      <c r="I37" s="4" t="n"/>
+      <c r="J37" s="4" t="n"/>
+      <c r="K37" s="4" t="n"/>
+      <c r="L37" s="4" t="n"/>
+      <c r="M37" s="4" t="n"/>
+      <c r="N37" s="4" t="n"/>
+      <c r="O37" s="4" t="n"/>
+      <c r="P37" s="4" t="n"/>
+      <c r="Q37" s="4" t="n"/>
+      <c r="R37" s="4" t="n"/>
+      <c r="S37" s="4" t="n"/>
+      <c r="T37" s="4" t="n"/>
       <c r="U37" s="4" t="n"/>
       <c r="V37" s="4" t="n"/>
       <c r="W37" s="4" t="n"/>
@@ -2482,28 +2452,58 @@
     </row>
     <row r="38">
       <c r="B38" t="n">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sonst. neutr. Ertr</t>
-        </is>
-      </c>
-      <c r="F38" s="4" t="n"/>
-      <c r="G38" s="4" t="n"/>
-      <c r="H38" s="4" t="n"/>
-      <c r="I38" s="4" t="n"/>
-      <c r="J38" s="4" t="n"/>
-      <c r="K38" s="4" t="n"/>
-      <c r="L38" s="4" t="n"/>
-      <c r="M38" s="4" t="n"/>
-      <c r="N38" s="4" t="n"/>
-      <c r="O38" s="4" t="n"/>
-      <c r="P38" s="4" t="n"/>
-      <c r="Q38" s="4" t="n"/>
-      <c r="R38" s="4" t="n"/>
-      <c r="S38" s="4" t="n"/>
-      <c r="T38" s="4" t="n"/>
+          <t>Zinserträge</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>288</v>
+      </c>
+      <c r="G38" s="4" t="n">
+        <v>294</v>
+      </c>
+      <c r="H38" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="I38" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="J38" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="K38" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="L38" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="M38" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="N38" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="O38" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="P38" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q38" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="R38" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="S38" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T38" s="4" t="n">
+        <v>300</v>
+      </c>
       <c r="U38" s="4" t="n"/>
       <c r="V38" s="4" t="n"/>
       <c r="W38" s="4" t="n"/>
@@ -2527,58 +2527,28 @@
     </row>
     <row r="39">
       <c r="B39" t="n">
-        <v>1330</v>
+        <v>1323</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Neutraler Ertrag</t>
-        </is>
-      </c>
-      <c r="F39" s="4" t="n">
-        <v>288</v>
-      </c>
-      <c r="G39" s="4" t="n">
-        <v>294</v>
-      </c>
-      <c r="H39" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="I39" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="J39" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="K39" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="L39" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="M39" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="N39" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="O39" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="P39" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q39" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="R39" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="S39" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="T39" s="4" t="n">
-        <v>300</v>
-      </c>
+          <t>Sonst. neutr. Ertr</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="n"/>
+      <c r="G39" s="4" t="n"/>
+      <c r="H39" s="4" t="n"/>
+      <c r="I39" s="4" t="n"/>
+      <c r="J39" s="4" t="n"/>
+      <c r="K39" s="4" t="n"/>
+      <c r="L39" s="4" t="n"/>
+      <c r="M39" s="4" t="n"/>
+      <c r="N39" s="4" t="n"/>
+      <c r="O39" s="4" t="n"/>
+      <c r="P39" s="4" t="n"/>
+      <c r="Q39" s="4" t="n"/>
+      <c r="R39" s="4" t="n"/>
+      <c r="S39" s="4" t="n"/>
+      <c r="T39" s="4" t="n"/>
       <c r="U39" s="4" t="n"/>
       <c r="V39" s="4" t="n"/>
       <c r="W39" s="4" t="n"/>
@@ -2602,23 +2572,58 @@
     </row>
     <row r="40">
       <c r="B40" t="n">
-        <v>1331</v>
-      </c>
-      <c r="F40" s="4" t="n"/>
-      <c r="G40" s="4" t="n"/>
-      <c r="H40" s="4" t="n"/>
-      <c r="I40" s="4" t="n"/>
-      <c r="J40" s="4" t="n"/>
-      <c r="K40" s="4" t="n"/>
-      <c r="L40" s="4" t="n"/>
-      <c r="M40" s="4" t="n"/>
-      <c r="N40" s="4" t="n"/>
-      <c r="O40" s="4" t="n"/>
-      <c r="P40" s="4" t="n"/>
-      <c r="Q40" s="4" t="n"/>
-      <c r="R40" s="4" t="n"/>
-      <c r="S40" s="4" t="n"/>
-      <c r="T40" s="4" t="n"/>
+        <v>1330</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Neutraler Ertrag</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="n">
+        <v>288</v>
+      </c>
+      <c r="G40" s="4" t="n">
+        <v>294</v>
+      </c>
+      <c r="H40" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="I40" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="J40" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="K40" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="L40" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="M40" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="N40" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="O40" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="P40" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q40" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="R40" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="S40" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T40" s="4" t="n">
+        <v>300</v>
+      </c>
       <c r="U40" s="4" t="n"/>
       <c r="V40" s="4" t="n"/>
       <c r="W40" s="4" t="n"/>
@@ -2642,7 +2647,7 @@
     </row>
     <row r="41">
       <c r="B41" t="n">
-        <v>1342</v>
+        <v>1331</v>
       </c>
       <c r="F41" s="4" t="n"/>
       <c r="G41" s="4" t="n"/>
@@ -2682,58 +2687,23 @@
     </row>
     <row r="42">
       <c r="B42" t="n">
-        <v>1345</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ergebnis vor Steuern</t>
-        </is>
-      </c>
-      <c r="F42" s="4" t="n">
-        <v>84384</v>
-      </c>
-      <c r="G42" s="4" t="n">
-        <v>86142</v>
-      </c>
-      <c r="H42" s="4" t="n">
-        <v>7325</v>
-      </c>
-      <c r="I42" s="4" t="n">
-        <v>7325</v>
-      </c>
-      <c r="J42" s="4" t="n">
-        <v>7325</v>
-      </c>
-      <c r="K42" s="4" t="n">
-        <v>7325</v>
-      </c>
-      <c r="L42" s="4" t="n">
-        <v>7325</v>
-      </c>
-      <c r="M42" s="4" t="n">
-        <v>7325</v>
-      </c>
-      <c r="N42" s="4" t="n">
-        <v>7325</v>
-      </c>
-      <c r="O42" s="4" t="n">
-        <v>7325</v>
-      </c>
-      <c r="P42" s="4" t="n">
-        <v>7325</v>
-      </c>
-      <c r="Q42" s="4" t="n">
-        <v>7325</v>
-      </c>
-      <c r="R42" s="4" t="n">
-        <v>7325</v>
-      </c>
-      <c r="S42" s="4" t="n">
-        <v>7325</v>
-      </c>
-      <c r="T42" s="4" t="n">
-        <v>87900</v>
-      </c>
+        <v>1342</v>
+      </c>
+      <c r="F42" s="4" t="n"/>
+      <c r="G42" s="4" t="n"/>
+      <c r="H42" s="4" t="n"/>
+      <c r="I42" s="4" t="n"/>
+      <c r="J42" s="4" t="n"/>
+      <c r="K42" s="4" t="n"/>
+      <c r="L42" s="4" t="n"/>
+      <c r="M42" s="4" t="n"/>
+      <c r="N42" s="4" t="n"/>
+      <c r="O42" s="4" t="n"/>
+      <c r="P42" s="4" t="n"/>
+      <c r="Q42" s="4" t="n"/>
+      <c r="R42" s="4" t="n"/>
+      <c r="S42" s="4" t="n"/>
+      <c r="T42" s="4" t="n"/>
       <c r="U42" s="4" t="n"/>
       <c r="V42" s="4" t="n"/>
       <c r="W42" s="4" t="n"/>
@@ -2757,23 +2727,58 @@
     </row>
     <row r="43">
       <c r="B43" t="n">
-        <v>1350</v>
-      </c>
-      <c r="F43" s="4" t="n"/>
-      <c r="G43" s="4" t="n"/>
-      <c r="H43" s="4" t="n"/>
-      <c r="I43" s="4" t="n"/>
-      <c r="J43" s="4" t="n"/>
-      <c r="K43" s="4" t="n"/>
-      <c r="L43" s="4" t="n"/>
-      <c r="M43" s="4" t="n"/>
-      <c r="N43" s="4" t="n"/>
-      <c r="O43" s="4" t="n"/>
-      <c r="P43" s="4" t="n"/>
-      <c r="Q43" s="4" t="n"/>
-      <c r="R43" s="4" t="n"/>
-      <c r="S43" s="4" t="n"/>
-      <c r="T43" s="4" t="n"/>
+        <v>1345</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ergebnis vor Steuern</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="n">
+        <v>84384</v>
+      </c>
+      <c r="G43" s="4" t="n">
+        <v>86142</v>
+      </c>
+      <c r="H43" s="4" t="n">
+        <v>7325</v>
+      </c>
+      <c r="I43" s="4" t="n">
+        <v>7325</v>
+      </c>
+      <c r="J43" s="4" t="n">
+        <v>7325</v>
+      </c>
+      <c r="K43" s="4" t="n">
+        <v>7325</v>
+      </c>
+      <c r="L43" s="4" t="n">
+        <v>7325</v>
+      </c>
+      <c r="M43" s="4" t="n">
+        <v>7325</v>
+      </c>
+      <c r="N43" s="4" t="n">
+        <v>7325</v>
+      </c>
+      <c r="O43" s="4" t="n">
+        <v>7325</v>
+      </c>
+      <c r="P43" s="4" t="n">
+        <v>7325</v>
+      </c>
+      <c r="Q43" s="4" t="n">
+        <v>7325</v>
+      </c>
+      <c r="R43" s="4" t="n">
+        <v>7325</v>
+      </c>
+      <c r="S43" s="4" t="n">
+        <v>7325</v>
+      </c>
+      <c r="T43" s="4" t="n">
+        <v>87900</v>
+      </c>
       <c r="U43" s="4" t="n"/>
       <c r="V43" s="4" t="n"/>
       <c r="W43" s="4" t="n"/>
@@ -2797,12 +2802,7 @@
     </row>
     <row r="44">
       <c r="B44" t="n">
-        <v>1351</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>außerordentlicher Ertrag</t>
-        </is>
+        <v>1350</v>
       </c>
       <c r="F44" s="4" t="n"/>
       <c r="G44" s="4" t="n"/>
@@ -2842,11 +2842,11 @@
     </row>
     <row r="45">
       <c r="B45" t="n">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>außerordentlicher Aufwand</t>
+          <t>außerordentlicher Ertrag</t>
         </is>
       </c>
       <c r="F45" s="4" t="n"/>
@@ -2887,58 +2887,28 @@
     </row>
     <row r="46">
       <c r="B46" t="n">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Außerordentliches Ergebnis</t>
-        </is>
-      </c>
-      <c r="F46" s="4" t="n">
-        <v>84384</v>
-      </c>
-      <c r="G46" s="4" t="n">
-        <v>86142</v>
-      </c>
-      <c r="H46" s="4" t="n">
-        <v>7325</v>
-      </c>
-      <c r="I46" s="4" t="n">
-        <v>7325</v>
-      </c>
-      <c r="J46" s="4" t="n">
-        <v>7325</v>
-      </c>
-      <c r="K46" s="4" t="n">
-        <v>7325</v>
-      </c>
-      <c r="L46" s="4" t="n">
-        <v>7325</v>
-      </c>
-      <c r="M46" s="4" t="n">
-        <v>7325</v>
-      </c>
-      <c r="N46" s="4" t="n">
-        <v>7325</v>
-      </c>
-      <c r="O46" s="4" t="n">
-        <v>7325</v>
-      </c>
-      <c r="P46" s="4" t="n">
-        <v>7325</v>
-      </c>
-      <c r="Q46" s="4" t="n">
-        <v>7325</v>
-      </c>
-      <c r="R46" s="4" t="n">
-        <v>7325</v>
-      </c>
-      <c r="S46" s="4" t="n">
-        <v>7325</v>
-      </c>
-      <c r="T46" s="4" t="n">
-        <v>87900</v>
-      </c>
+          <t>außerordentlicher Aufwand</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="n"/>
+      <c r="G46" s="4" t="n"/>
+      <c r="H46" s="4" t="n"/>
+      <c r="I46" s="4" t="n"/>
+      <c r="J46" s="4" t="n"/>
+      <c r="K46" s="4" t="n"/>
+      <c r="L46" s="4" t="n"/>
+      <c r="M46" s="4" t="n"/>
+      <c r="N46" s="4" t="n"/>
+      <c r="O46" s="4" t="n"/>
+      <c r="P46" s="4" t="n"/>
+      <c r="Q46" s="4" t="n"/>
+      <c r="R46" s="4" t="n"/>
+      <c r="S46" s="4" t="n"/>
+      <c r="T46" s="4" t="n"/>
       <c r="U46" s="4" t="n"/>
       <c r="V46" s="4" t="n"/>
       <c r="W46" s="4" t="n"/>
@@ -2962,23 +2932,58 @@
     </row>
     <row r="47">
       <c r="B47" t="n">
-        <v>1354</v>
-      </c>
-      <c r="F47" s="4" t="n"/>
-      <c r="G47" s="4" t="n"/>
-      <c r="H47" s="4" t="n"/>
-      <c r="I47" s="4" t="n"/>
-      <c r="J47" s="4" t="n"/>
-      <c r="K47" s="4" t="n"/>
-      <c r="L47" s="4" t="n"/>
-      <c r="M47" s="4" t="n"/>
-      <c r="N47" s="4" t="n"/>
-      <c r="O47" s="4" t="n"/>
-      <c r="P47" s="4" t="n"/>
-      <c r="Q47" s="4" t="n"/>
-      <c r="R47" s="4" t="n"/>
-      <c r="S47" s="4" t="n"/>
-      <c r="T47" s="4" t="n"/>
+        <v>1353</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Außerordentliches Ergebnis</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="n">
+        <v>84384</v>
+      </c>
+      <c r="G47" s="4" t="n">
+        <v>86142</v>
+      </c>
+      <c r="H47" s="4" t="n">
+        <v>7325</v>
+      </c>
+      <c r="I47" s="4" t="n">
+        <v>7325</v>
+      </c>
+      <c r="J47" s="4" t="n">
+        <v>7325</v>
+      </c>
+      <c r="K47" s="4" t="n">
+        <v>7325</v>
+      </c>
+      <c r="L47" s="4" t="n">
+        <v>7325</v>
+      </c>
+      <c r="M47" s="4" t="n">
+        <v>7325</v>
+      </c>
+      <c r="N47" s="4" t="n">
+        <v>7325</v>
+      </c>
+      <c r="O47" s="4" t="n">
+        <v>7325</v>
+      </c>
+      <c r="P47" s="4" t="n">
+        <v>7325</v>
+      </c>
+      <c r="Q47" s="4" t="n">
+        <v>7325</v>
+      </c>
+      <c r="R47" s="4" t="n">
+        <v>7325</v>
+      </c>
+      <c r="S47" s="4" t="n">
+        <v>7325</v>
+      </c>
+      <c r="T47" s="4" t="n">
+        <v>87900</v>
+      </c>
       <c r="U47" s="4" t="n"/>
       <c r="V47" s="4" t="n"/>
       <c r="W47" s="4" t="n"/>
@@ -3002,12 +3007,7 @@
     </row>
     <row r="48">
       <c r="B48" t="n">
-        <v>1355</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Steuern Eink.u.Ertr</t>
-        </is>
+        <v>1354</v>
       </c>
       <c r="F48" s="4" t="n"/>
       <c r="G48" s="4" t="n"/>
@@ -3047,7 +3047,12 @@
     </row>
     <row r="49">
       <c r="B49" t="n">
-        <v>1360</v>
+        <v>1355</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Steuern Eink.u.Ertr</t>
+        </is>
       </c>
       <c r="F49" s="4" t="n"/>
       <c r="G49" s="4" t="n"/>
@@ -3087,58 +3092,23 @@
     </row>
     <row r="50">
       <c r="B50" t="n">
-        <v>1380</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Vorläufiges Ergebnis</t>
-        </is>
-      </c>
-      <c r="F50" s="4" t="n">
-        <v>84384</v>
-      </c>
-      <c r="G50" s="4" t="n">
-        <v>86142</v>
-      </c>
-      <c r="H50" s="4" t="n">
-        <v>7325</v>
-      </c>
-      <c r="I50" s="4" t="n">
-        <v>7325</v>
-      </c>
-      <c r="J50" s="4" t="n">
-        <v>7325</v>
-      </c>
-      <c r="K50" s="4" t="n">
-        <v>7325</v>
-      </c>
-      <c r="L50" s="4" t="n">
-        <v>7325</v>
-      </c>
-      <c r="M50" s="4" t="n">
-        <v>7325</v>
-      </c>
-      <c r="N50" s="4" t="n">
-        <v>7325</v>
-      </c>
-      <c r="O50" s="4" t="n">
-        <v>7325</v>
-      </c>
-      <c r="P50" s="4" t="n">
-        <v>7325</v>
-      </c>
-      <c r="Q50" s="4" t="n">
-        <v>7325</v>
-      </c>
-      <c r="R50" s="4" t="n">
-        <v>7325</v>
-      </c>
-      <c r="S50" s="4" t="n">
-        <v>7325</v>
-      </c>
-      <c r="T50" s="4" t="n">
-        <v>87900</v>
-      </c>
+        <v>1360</v>
+      </c>
+      <c r="F50" s="4" t="n"/>
+      <c r="G50" s="4" t="n"/>
+      <c r="H50" s="4" t="n"/>
+      <c r="I50" s="4" t="n"/>
+      <c r="J50" s="4" t="n"/>
+      <c r="K50" s="4" t="n"/>
+      <c r="L50" s="4" t="n"/>
+      <c r="M50" s="4" t="n"/>
+      <c r="N50" s="4" t="n"/>
+      <c r="O50" s="4" t="n"/>
+      <c r="P50" s="4" t="n"/>
+      <c r="Q50" s="4" t="n"/>
+      <c r="R50" s="4" t="n"/>
+      <c r="S50" s="4" t="n"/>
+      <c r="T50" s="4" t="n"/>
       <c r="U50" s="4" t="n"/>
       <c r="V50" s="4" t="n"/>
       <c r="W50" s="4" t="n"/>
@@ -3160,6 +3130,81 @@
       <c r="AM50" s="4" t="n"/>
       <c r="AN50" s="4" t="n"/>
     </row>
+    <row r="51">
+      <c r="B51" t="n">
+        <v>1380</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Vorläufiges Ergebnis</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="n">
+        <v>84384</v>
+      </c>
+      <c r="G51" s="4" t="n">
+        <v>86142</v>
+      </c>
+      <c r="H51" s="4" t="n">
+        <v>7325</v>
+      </c>
+      <c r="I51" s="4" t="n">
+        <v>7325</v>
+      </c>
+      <c r="J51" s="4" t="n">
+        <v>7325</v>
+      </c>
+      <c r="K51" s="4" t="n">
+        <v>7325</v>
+      </c>
+      <c r="L51" s="4" t="n">
+        <v>7325</v>
+      </c>
+      <c r="M51" s="4" t="n">
+        <v>7325</v>
+      </c>
+      <c r="N51" s="4" t="n">
+        <v>7325</v>
+      </c>
+      <c r="O51" s="4" t="n">
+        <v>7325</v>
+      </c>
+      <c r="P51" s="4" t="n">
+        <v>7325</v>
+      </c>
+      <c r="Q51" s="4" t="n">
+        <v>7325</v>
+      </c>
+      <c r="R51" s="4" t="n">
+        <v>7325</v>
+      </c>
+      <c r="S51" s="4" t="n">
+        <v>7325</v>
+      </c>
+      <c r="T51" s="4" t="n">
+        <v>87900</v>
+      </c>
+      <c r="U51" s="4" t="n"/>
+      <c r="V51" s="4" t="n"/>
+      <c r="W51" s="4" t="n"/>
+      <c r="X51" s="4" t="n"/>
+      <c r="Y51" s="4" t="n"/>
+      <c r="Z51" s="4" t="n"/>
+      <c r="AA51" s="4" t="n"/>
+      <c r="AB51" s="4" t="n"/>
+      <c r="AC51" s="4" t="n"/>
+      <c r="AD51" s="4" t="n"/>
+      <c r="AE51" s="4" t="n"/>
+      <c r="AF51" s="4" t="n"/>
+      <c r="AG51" s="4" t="n"/>
+      <c r="AH51" s="4" t="n"/>
+      <c r="AI51" s="4" t="n"/>
+      <c r="AJ51" s="4" t="n"/>
+      <c r="AK51" s="4" t="n"/>
+      <c r="AL51" s="4" t="n"/>
+      <c r="AM51" s="4" t="n"/>
+      <c r="AN51" s="4" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3171,7 +3216,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:AN61"/>
+  <dimension ref="B2:AN62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="3" max="3"/>
@@ -4263,11 +4308,11 @@
     </row>
     <row r="23">
       <c r="B23" t="n">
-        <v>1180</v>
+        <v>1160</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Kfz-Kosten (o. St.)</t>
+          <t>Besondere Kosten</t>
         </is>
       </c>
       <c r="F23" s="4" t="n"/>
@@ -4308,11 +4353,11 @@
     </row>
     <row r="24">
       <c r="B24" t="n">
-        <v>1200</v>
+        <v>1180</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Werbe-/Reisekosten</t>
+          <t>Kfz-Kosten (o. St.)</t>
         </is>
       </c>
       <c r="F24" s="4" t="n"/>
@@ -4353,11 +4398,11 @@
     </row>
     <row r="25">
       <c r="B25" t="n">
-        <v>1220</v>
+        <v>1200</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Kosten Warenabgabe</t>
+          <t>Werbe-/Reisekosten</t>
         </is>
       </c>
       <c r="F25" s="4" t="n"/>
@@ -4398,58 +4443,28 @@
     </row>
     <row r="26">
       <c r="B26" t="n">
-        <v>1240</v>
+        <v>1220</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Abschreibungen</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="n">
-        <v>15360</v>
-      </c>
-      <c r="G26" s="4" t="n">
-        <v>15680</v>
-      </c>
-      <c r="H26" s="4" t="n">
-        <v>1333.33</v>
-      </c>
-      <c r="I26" s="4" t="n">
-        <v>1333.33</v>
-      </c>
-      <c r="J26" s="4" t="n">
-        <v>1333.33</v>
-      </c>
-      <c r="K26" s="4" t="n">
-        <v>1333.33</v>
-      </c>
-      <c r="L26" s="4" t="n">
-        <v>1333.33</v>
-      </c>
-      <c r="M26" s="4" t="n">
-        <v>1333.33</v>
-      </c>
-      <c r="N26" s="4" t="n">
-        <v>1333.33</v>
-      </c>
-      <c r="O26" s="4" t="n">
-        <v>1333.33</v>
-      </c>
-      <c r="P26" s="4" t="n">
-        <v>1333.33</v>
-      </c>
-      <c r="Q26" s="4" t="n">
-        <v>1333.33</v>
-      </c>
-      <c r="R26" s="4" t="n">
-        <v>1333.33</v>
-      </c>
-      <c r="S26" s="4" t="n">
-        <v>1333.33</v>
-      </c>
-      <c r="T26" s="4" t="n">
-        <v>16000</v>
-      </c>
+          <t>Kosten Warenabgabe</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="n"/>
+      <c r="G26" s="4" t="n"/>
+      <c r="H26" s="4" t="n"/>
+      <c r="I26" s="4" t="n"/>
+      <c r="J26" s="4" t="n"/>
+      <c r="K26" s="4" t="n"/>
+      <c r="L26" s="4" t="n"/>
+      <c r="M26" s="4" t="n"/>
+      <c r="N26" s="4" t="n"/>
+      <c r="O26" s="4" t="n"/>
+      <c r="P26" s="4" t="n"/>
+      <c r="Q26" s="4" t="n"/>
+      <c r="R26" s="4" t="n"/>
+      <c r="S26" s="4" t="n"/>
+      <c r="T26" s="4" t="n"/>
       <c r="U26" s="4" t="n"/>
       <c r="V26" s="4" t="n"/>
       <c r="W26" s="4" t="n"/>
@@ -4473,57 +4488,57 @@
     </row>
     <row r="27">
       <c r="B27" t="n">
-        <v>1250</v>
+        <v>1240</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Reparatur/Instandh.</t>
+          <t>Abschreibungen</t>
         </is>
       </c>
       <c r="F27" s="4" t="n">
-        <v>7680</v>
+        <v>15360</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>7840</v>
+        <v>15680</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>666.67</v>
+        <v>1333.33</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>666.67</v>
+        <v>1333.33</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>666.67</v>
+        <v>1333.33</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>666.67</v>
+        <v>1333.33</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>666.67</v>
+        <v>1333.33</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>666.67</v>
+        <v>1333.33</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>666.67</v>
+        <v>1333.33</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>666.67</v>
+        <v>1333.33</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>666.67</v>
+        <v>1333.33</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>666.67</v>
+        <v>1333.33</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>666.67</v>
+        <v>1333.33</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>666.67</v>
+        <v>1333.33</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>8000</v>
+        <v>16000</v>
       </c>
       <c r="U27" s="4" t="n"/>
       <c r="V27" s="4" t="n"/>
@@ -4548,57 +4563,57 @@
     </row>
     <row r="28">
       <c r="B28" t="n">
-        <v>1260</v>
+        <v>1250</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sonstige Kosten</t>
+          <t>Reparatur/Instandh.</t>
         </is>
       </c>
       <c r="F28" s="4" t="n">
-        <v>576</v>
+        <v>7680</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>588</v>
+        <v>7840</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>50</v>
+        <v>666.67</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>50</v>
+        <v>666.67</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>50</v>
+        <v>666.67</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>50</v>
+        <v>666.67</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>50</v>
+        <v>666.67</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>50</v>
+        <v>666.67</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>50</v>
+        <v>666.67</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>50</v>
+        <v>666.67</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>50</v>
+        <v>666.67</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>50</v>
+        <v>666.67</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>50</v>
+        <v>666.67</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>50</v>
+        <v>666.67</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>600</v>
+        <v>8000</v>
       </c>
       <c r="U28" s="4" t="n"/>
       <c r="V28" s="4" t="n"/>
@@ -4623,57 +4638,57 @@
     </row>
     <row r="29">
       <c r="B29" t="n">
-        <v>1280</v>
+        <v>1260</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Gesamtkosten</t>
+          <t>Sonstige Kosten</t>
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>26496</v>
+        <v>576</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>27048</v>
+        <v>588</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>2300</v>
+        <v>50</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>2300</v>
+        <v>50</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>2300</v>
+        <v>50</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>2300</v>
+        <v>50</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>2300</v>
+        <v>50</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>2300</v>
+        <v>50</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>2300</v>
+        <v>50</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>2300</v>
+        <v>50</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>2300</v>
+        <v>50</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>2300</v>
+        <v>50</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>2300</v>
+        <v>50</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>2300</v>
+        <v>50</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>27600</v>
+        <v>600</v>
       </c>
       <c r="U29" s="4" t="n"/>
       <c r="V29" s="4" t="n"/>
@@ -4698,23 +4713,58 @@
     </row>
     <row r="30">
       <c r="B30" t="n">
-        <v>1290</v>
-      </c>
-      <c r="F30" s="4" t="n"/>
-      <c r="G30" s="4" t="n"/>
-      <c r="H30" s="4" t="n"/>
-      <c r="I30" s="4" t="n"/>
-      <c r="J30" s="4" t="n"/>
-      <c r="K30" s="4" t="n"/>
-      <c r="L30" s="4" t="n"/>
-      <c r="M30" s="4" t="n"/>
-      <c r="N30" s="4" t="n"/>
-      <c r="O30" s="4" t="n"/>
-      <c r="P30" s="4" t="n"/>
-      <c r="Q30" s="4" t="n"/>
-      <c r="R30" s="4" t="n"/>
-      <c r="S30" s="4" t="n"/>
-      <c r="T30" s="4" t="n"/>
+        <v>1280</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Gesamtkosten</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>26496</v>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>27048</v>
+      </c>
+      <c r="H30" s="4" t="n">
+        <v>2300</v>
+      </c>
+      <c r="I30" s="4" t="n">
+        <v>2300</v>
+      </c>
+      <c r="J30" s="4" t="n">
+        <v>2300</v>
+      </c>
+      <c r="K30" s="4" t="n">
+        <v>2300</v>
+      </c>
+      <c r="L30" s="4" t="n">
+        <v>2300</v>
+      </c>
+      <c r="M30" s="4" t="n">
+        <v>2300</v>
+      </c>
+      <c r="N30" s="4" t="n">
+        <v>2300</v>
+      </c>
+      <c r="O30" s="4" t="n">
+        <v>2300</v>
+      </c>
+      <c r="P30" s="4" t="n">
+        <v>2300</v>
+      </c>
+      <c r="Q30" s="4" t="n">
+        <v>2300</v>
+      </c>
+      <c r="R30" s="4" t="n">
+        <v>2300</v>
+      </c>
+      <c r="S30" s="4" t="n">
+        <v>2300</v>
+      </c>
+      <c r="T30" s="4" t="n">
+        <v>27600</v>
+      </c>
       <c r="U30" s="4" t="n"/>
       <c r="V30" s="4" t="n"/>
       <c r="W30" s="4" t="n"/>
@@ -4738,58 +4788,23 @@
     </row>
     <row r="31">
       <c r="B31" t="n">
-        <v>1300</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Betriebsergebnis</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="n">
-        <v>31104</v>
-      </c>
-      <c r="G31" s="4" t="n">
-        <v>31752</v>
-      </c>
-      <c r="H31" s="4" t="n">
-        <v>2700</v>
-      </c>
-      <c r="I31" s="4" t="n">
-        <v>2700</v>
-      </c>
-      <c r="J31" s="4" t="n">
-        <v>2700</v>
-      </c>
-      <c r="K31" s="4" t="n">
-        <v>2700</v>
-      </c>
-      <c r="L31" s="4" t="n">
-        <v>2700</v>
-      </c>
-      <c r="M31" s="4" t="n">
-        <v>2700</v>
-      </c>
-      <c r="N31" s="4" t="n">
-        <v>2700</v>
-      </c>
-      <c r="O31" s="4" t="n">
-        <v>2700</v>
-      </c>
-      <c r="P31" s="4" t="n">
-        <v>2700</v>
-      </c>
-      <c r="Q31" s="4" t="n">
-        <v>2700</v>
-      </c>
-      <c r="R31" s="4" t="n">
-        <v>2700</v>
-      </c>
-      <c r="S31" s="4" t="n">
-        <v>2700</v>
-      </c>
-      <c r="T31" s="4" t="n">
-        <v>32400</v>
-      </c>
+        <v>1290</v>
+      </c>
+      <c r="F31" s="4" t="n"/>
+      <c r="G31" s="4" t="n"/>
+      <c r="H31" s="4" t="n"/>
+      <c r="I31" s="4" t="n"/>
+      <c r="J31" s="4" t="n"/>
+      <c r="K31" s="4" t="n"/>
+      <c r="L31" s="4" t="n"/>
+      <c r="M31" s="4" t="n"/>
+      <c r="N31" s="4" t="n"/>
+      <c r="O31" s="4" t="n"/>
+      <c r="P31" s="4" t="n"/>
+      <c r="Q31" s="4" t="n"/>
+      <c r="R31" s="4" t="n"/>
+      <c r="S31" s="4" t="n"/>
+      <c r="T31" s="4" t="n"/>
       <c r="U31" s="4" t="n"/>
       <c r="V31" s="4" t="n"/>
       <c r="W31" s="4" t="n"/>
@@ -4813,23 +4828,58 @@
     </row>
     <row r="32">
       <c r="B32" t="n">
-        <v>1301</v>
-      </c>
-      <c r="F32" s="4" t="n"/>
-      <c r="G32" s="4" t="n"/>
-      <c r="H32" s="4" t="n"/>
-      <c r="I32" s="4" t="n"/>
-      <c r="J32" s="4" t="n"/>
-      <c r="K32" s="4" t="n"/>
-      <c r="L32" s="4" t="n"/>
-      <c r="M32" s="4" t="n"/>
-      <c r="N32" s="4" t="n"/>
-      <c r="O32" s="4" t="n"/>
-      <c r="P32" s="4" t="n"/>
-      <c r="Q32" s="4" t="n"/>
-      <c r="R32" s="4" t="n"/>
-      <c r="S32" s="4" t="n"/>
-      <c r="T32" s="4" t="n"/>
+        <v>1300</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Betriebsergebnis</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>31104</v>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>31752</v>
+      </c>
+      <c r="H32" s="4" t="n">
+        <v>2700</v>
+      </c>
+      <c r="I32" s="4" t="n">
+        <v>2700</v>
+      </c>
+      <c r="J32" s="4" t="n">
+        <v>2700</v>
+      </c>
+      <c r="K32" s="4" t="n">
+        <v>2700</v>
+      </c>
+      <c r="L32" s="4" t="n">
+        <v>2700</v>
+      </c>
+      <c r="M32" s="4" t="n">
+        <v>2700</v>
+      </c>
+      <c r="N32" s="4" t="n">
+        <v>2700</v>
+      </c>
+      <c r="O32" s="4" t="n">
+        <v>2700</v>
+      </c>
+      <c r="P32" s="4" t="n">
+        <v>2700</v>
+      </c>
+      <c r="Q32" s="4" t="n">
+        <v>2700</v>
+      </c>
+      <c r="R32" s="4" t="n">
+        <v>2700</v>
+      </c>
+      <c r="S32" s="4" t="n">
+        <v>2700</v>
+      </c>
+      <c r="T32" s="4" t="n">
+        <v>32400</v>
+      </c>
       <c r="U32" s="4" t="n"/>
       <c r="V32" s="4" t="n"/>
       <c r="W32" s="4" t="n"/>
@@ -4853,58 +4903,23 @@
     </row>
     <row r="33">
       <c r="B33" t="n">
-        <v>1310</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Zinsaufwand</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="n">
-        <v>3840</v>
-      </c>
-      <c r="G33" s="4" t="n">
-        <v>3920</v>
-      </c>
-      <c r="H33" s="4" t="n">
-        <v>333.33</v>
-      </c>
-      <c r="I33" s="4" t="n">
-        <v>333.33</v>
-      </c>
-      <c r="J33" s="4" t="n">
-        <v>333.33</v>
-      </c>
-      <c r="K33" s="4" t="n">
-        <v>333.33</v>
-      </c>
-      <c r="L33" s="4" t="n">
-        <v>333.33</v>
-      </c>
-      <c r="M33" s="4" t="n">
-        <v>333.33</v>
-      </c>
-      <c r="N33" s="4" t="n">
-        <v>333.33</v>
-      </c>
-      <c r="O33" s="4" t="n">
-        <v>333.33</v>
-      </c>
-      <c r="P33" s="4" t="n">
-        <v>333.33</v>
-      </c>
-      <c r="Q33" s="4" t="n">
-        <v>333.33</v>
-      </c>
-      <c r="R33" s="4" t="n">
-        <v>333.33</v>
-      </c>
-      <c r="S33" s="4" t="n">
-        <v>333.33</v>
-      </c>
-      <c r="T33" s="4" t="n">
-        <v>4000</v>
-      </c>
+        <v>1301</v>
+      </c>
+      <c r="F33" s="4" t="n"/>
+      <c r="G33" s="4" t="n"/>
+      <c r="H33" s="4" t="n"/>
+      <c r="I33" s="4" t="n"/>
+      <c r="J33" s="4" t="n"/>
+      <c r="K33" s="4" t="n"/>
+      <c r="L33" s="4" t="n"/>
+      <c r="M33" s="4" t="n"/>
+      <c r="N33" s="4" t="n"/>
+      <c r="O33" s="4" t="n"/>
+      <c r="P33" s="4" t="n"/>
+      <c r="Q33" s="4" t="n"/>
+      <c r="R33" s="4" t="n"/>
+      <c r="S33" s="4" t="n"/>
+      <c r="T33" s="4" t="n"/>
       <c r="U33" s="4" t="n"/>
       <c r="V33" s="4" t="n"/>
       <c r="W33" s="4" t="n"/>
@@ -4928,28 +4943,58 @@
     </row>
     <row r="34">
       <c r="B34" t="n">
-        <v>1312</v>
+        <v>1310</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sonst. neutr. Aufw</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="n"/>
-      <c r="G34" s="4" t="n"/>
-      <c r="H34" s="4" t="n"/>
-      <c r="I34" s="4" t="n"/>
-      <c r="J34" s="4" t="n"/>
-      <c r="K34" s="4" t="n"/>
-      <c r="L34" s="4" t="n"/>
-      <c r="M34" s="4" t="n"/>
-      <c r="N34" s="4" t="n"/>
-      <c r="O34" s="4" t="n"/>
-      <c r="P34" s="4" t="n"/>
-      <c r="Q34" s="4" t="n"/>
-      <c r="R34" s="4" t="n"/>
-      <c r="S34" s="4" t="n"/>
-      <c r="T34" s="4" t="n"/>
+          <t>Zinsaufwand</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>3840</v>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>3920</v>
+      </c>
+      <c r="H34" s="4" t="n">
+        <v>333.33</v>
+      </c>
+      <c r="I34" s="4" t="n">
+        <v>333.33</v>
+      </c>
+      <c r="J34" s="4" t="n">
+        <v>333.33</v>
+      </c>
+      <c r="K34" s="4" t="n">
+        <v>333.33</v>
+      </c>
+      <c r="L34" s="4" t="n">
+        <v>333.33</v>
+      </c>
+      <c r="M34" s="4" t="n">
+        <v>333.33</v>
+      </c>
+      <c r="N34" s="4" t="n">
+        <v>333.33</v>
+      </c>
+      <c r="O34" s="4" t="n">
+        <v>333.33</v>
+      </c>
+      <c r="P34" s="4" t="n">
+        <v>333.33</v>
+      </c>
+      <c r="Q34" s="4" t="n">
+        <v>333.33</v>
+      </c>
+      <c r="R34" s="4" t="n">
+        <v>333.33</v>
+      </c>
+      <c r="S34" s="4" t="n">
+        <v>333.33</v>
+      </c>
+      <c r="T34" s="4" t="n">
+        <v>4000</v>
+      </c>
       <c r="U34" s="4" t="n"/>
       <c r="V34" s="4" t="n"/>
       <c r="W34" s="4" t="n"/>
@@ -4973,58 +5018,28 @@
     </row>
     <row r="35">
       <c r="B35" t="n">
-        <v>1320</v>
+        <v>1312</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Neutraler Aufwand</t>
-        </is>
-      </c>
-      <c r="F35" s="4" t="n">
-        <v>3840</v>
-      </c>
-      <c r="G35" s="4" t="n">
-        <v>3920</v>
-      </c>
-      <c r="H35" s="4" t="n">
-        <v>333.33</v>
-      </c>
-      <c r="I35" s="4" t="n">
-        <v>333.33</v>
-      </c>
-      <c r="J35" s="4" t="n">
-        <v>333.33</v>
-      </c>
-      <c r="K35" s="4" t="n">
-        <v>333.33</v>
-      </c>
-      <c r="L35" s="4" t="n">
-        <v>333.33</v>
-      </c>
-      <c r="M35" s="4" t="n">
-        <v>333.33</v>
-      </c>
-      <c r="N35" s="4" t="n">
-        <v>333.33</v>
-      </c>
-      <c r="O35" s="4" t="n">
-        <v>333.33</v>
-      </c>
-      <c r="P35" s="4" t="n">
-        <v>333.33</v>
-      </c>
-      <c r="Q35" s="4" t="n">
-        <v>333.33</v>
-      </c>
-      <c r="R35" s="4" t="n">
-        <v>333.33</v>
-      </c>
-      <c r="S35" s="4" t="n">
-        <v>333.33</v>
-      </c>
-      <c r="T35" s="4" t="n">
-        <v>4000</v>
-      </c>
+          <t>Sonst. neutr. Aufw</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="n"/>
+      <c r="G35" s="4" t="n"/>
+      <c r="H35" s="4" t="n"/>
+      <c r="I35" s="4" t="n"/>
+      <c r="J35" s="4" t="n"/>
+      <c r="K35" s="4" t="n"/>
+      <c r="L35" s="4" t="n"/>
+      <c r="M35" s="4" t="n"/>
+      <c r="N35" s="4" t="n"/>
+      <c r="O35" s="4" t="n"/>
+      <c r="P35" s="4" t="n"/>
+      <c r="Q35" s="4" t="n"/>
+      <c r="R35" s="4" t="n"/>
+      <c r="S35" s="4" t="n"/>
+      <c r="T35" s="4" t="n"/>
       <c r="U35" s="4" t="n"/>
       <c r="V35" s="4" t="n"/>
       <c r="W35" s="4" t="n"/>
@@ -5048,23 +5063,58 @@
     </row>
     <row r="36">
       <c r="B36" t="n">
-        <v>1321</v>
-      </c>
-      <c r="F36" s="4" t="n"/>
-      <c r="G36" s="4" t="n"/>
-      <c r="H36" s="4" t="n"/>
-      <c r="I36" s="4" t="n"/>
-      <c r="J36" s="4" t="n"/>
-      <c r="K36" s="4" t="n"/>
-      <c r="L36" s="4" t="n"/>
-      <c r="M36" s="4" t="n"/>
-      <c r="N36" s="4" t="n"/>
-      <c r="O36" s="4" t="n"/>
-      <c r="P36" s="4" t="n"/>
-      <c r="Q36" s="4" t="n"/>
-      <c r="R36" s="4" t="n"/>
-      <c r="S36" s="4" t="n"/>
-      <c r="T36" s="4" t="n"/>
+        <v>1320</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Neutraler Aufwand</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>3840</v>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>3920</v>
+      </c>
+      <c r="H36" s="4" t="n">
+        <v>333.33</v>
+      </c>
+      <c r="I36" s="4" t="n">
+        <v>333.33</v>
+      </c>
+      <c r="J36" s="4" t="n">
+        <v>333.33</v>
+      </c>
+      <c r="K36" s="4" t="n">
+        <v>333.33</v>
+      </c>
+      <c r="L36" s="4" t="n">
+        <v>333.33</v>
+      </c>
+      <c r="M36" s="4" t="n">
+        <v>333.33</v>
+      </c>
+      <c r="N36" s="4" t="n">
+        <v>333.33</v>
+      </c>
+      <c r="O36" s="4" t="n">
+        <v>333.33</v>
+      </c>
+      <c r="P36" s="4" t="n">
+        <v>333.33</v>
+      </c>
+      <c r="Q36" s="4" t="n">
+        <v>333.33</v>
+      </c>
+      <c r="R36" s="4" t="n">
+        <v>333.33</v>
+      </c>
+      <c r="S36" s="4" t="n">
+        <v>333.33</v>
+      </c>
+      <c r="T36" s="4" t="n">
+        <v>4000</v>
+      </c>
       <c r="U36" s="4" t="n"/>
       <c r="V36" s="4" t="n"/>
       <c r="W36" s="4" t="n"/>
@@ -5088,12 +5138,7 @@
     </row>
     <row r="37">
       <c r="B37" t="n">
-        <v>1322</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Zinserträge</t>
-        </is>
+        <v>1321</v>
       </c>
       <c r="F37" s="4" t="n"/>
       <c r="G37" s="4" t="n"/>
@@ -5133,11 +5178,11 @@
     </row>
     <row r="38">
       <c r="B38" t="n">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sonst. neutr. Ertr</t>
+          <t>Zinserträge</t>
         </is>
       </c>
       <c r="F38" s="4" t="n"/>
@@ -5178,11 +5223,11 @@
     </row>
     <row r="39">
       <c r="B39" t="n">
-        <v>1330</v>
+        <v>1323</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Neutraler Ertrag</t>
+          <t>Sonst. neutr. Ertr</t>
         </is>
       </c>
       <c r="F39" s="4" t="n"/>
@@ -5223,7 +5268,12 @@
     </row>
     <row r="40">
       <c r="B40" t="n">
-        <v>1331</v>
+        <v>1330</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Neutraler Ertrag</t>
+        </is>
       </c>
       <c r="F40" s="4" t="n"/>
       <c r="G40" s="4" t="n"/>
@@ -5263,7 +5313,7 @@
     </row>
     <row r="41">
       <c r="B41" t="n">
-        <v>1342</v>
+        <v>1331</v>
       </c>
       <c r="F41" s="4" t="n"/>
       <c r="G41" s="4" t="n"/>
@@ -5303,58 +5353,23 @@
     </row>
     <row r="42">
       <c r="B42" t="n">
-        <v>1345</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ergebnis vor Steuern</t>
-        </is>
-      </c>
-      <c r="F42" s="4" t="n">
-        <v>27264</v>
-      </c>
-      <c r="G42" s="4" t="n">
-        <v>27832</v>
-      </c>
-      <c r="H42" s="4" t="n">
-        <v>2366.67</v>
-      </c>
-      <c r="I42" s="4" t="n">
-        <v>2366.67</v>
-      </c>
-      <c r="J42" s="4" t="n">
-        <v>2366.67</v>
-      </c>
-      <c r="K42" s="4" t="n">
-        <v>2366.67</v>
-      </c>
-      <c r="L42" s="4" t="n">
-        <v>2366.67</v>
-      </c>
-      <c r="M42" s="4" t="n">
-        <v>2366.67</v>
-      </c>
-      <c r="N42" s="4" t="n">
-        <v>2366.67</v>
-      </c>
-      <c r="O42" s="4" t="n">
-        <v>2366.67</v>
-      </c>
-      <c r="P42" s="4" t="n">
-        <v>2366.67</v>
-      </c>
-      <c r="Q42" s="4" t="n">
-        <v>2366.67</v>
-      </c>
-      <c r="R42" s="4" t="n">
-        <v>2366.67</v>
-      </c>
-      <c r="S42" s="4" t="n">
-        <v>2366.67</v>
-      </c>
-      <c r="T42" s="4" t="n">
-        <v>28400</v>
-      </c>
+        <v>1342</v>
+      </c>
+      <c r="F42" s="4" t="n"/>
+      <c r="G42" s="4" t="n"/>
+      <c r="H42" s="4" t="n"/>
+      <c r="I42" s="4" t="n"/>
+      <c r="J42" s="4" t="n"/>
+      <c r="K42" s="4" t="n"/>
+      <c r="L42" s="4" t="n"/>
+      <c r="M42" s="4" t="n"/>
+      <c r="N42" s="4" t="n"/>
+      <c r="O42" s="4" t="n"/>
+      <c r="P42" s="4" t="n"/>
+      <c r="Q42" s="4" t="n"/>
+      <c r="R42" s="4" t="n"/>
+      <c r="S42" s="4" t="n"/>
+      <c r="T42" s="4" t="n"/>
       <c r="U42" s="4" t="n"/>
       <c r="V42" s="4" t="n"/>
       <c r="W42" s="4" t="n"/>
@@ -5378,23 +5393,58 @@
     </row>
     <row r="43">
       <c r="B43" t="n">
-        <v>1350</v>
-      </c>
-      <c r="F43" s="4" t="n"/>
-      <c r="G43" s="4" t="n"/>
-      <c r="H43" s="4" t="n"/>
-      <c r="I43" s="4" t="n"/>
-      <c r="J43" s="4" t="n"/>
-      <c r="K43" s="4" t="n"/>
-      <c r="L43" s="4" t="n"/>
-      <c r="M43" s="4" t="n"/>
-      <c r="N43" s="4" t="n"/>
-      <c r="O43" s="4" t="n"/>
-      <c r="P43" s="4" t="n"/>
-      <c r="Q43" s="4" t="n"/>
-      <c r="R43" s="4" t="n"/>
-      <c r="S43" s="4" t="n"/>
-      <c r="T43" s="4" t="n"/>
+        <v>1345</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ergebnis vor Steuern</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="n">
+        <v>27264</v>
+      </c>
+      <c r="G43" s="4" t="n">
+        <v>27832</v>
+      </c>
+      <c r="H43" s="4" t="n">
+        <v>2366.67</v>
+      </c>
+      <c r="I43" s="4" t="n">
+        <v>2366.67</v>
+      </c>
+      <c r="J43" s="4" t="n">
+        <v>2366.67</v>
+      </c>
+      <c r="K43" s="4" t="n">
+        <v>2366.67</v>
+      </c>
+      <c r="L43" s="4" t="n">
+        <v>2366.67</v>
+      </c>
+      <c r="M43" s="4" t="n">
+        <v>2366.67</v>
+      </c>
+      <c r="N43" s="4" t="n">
+        <v>2366.67</v>
+      </c>
+      <c r="O43" s="4" t="n">
+        <v>2366.67</v>
+      </c>
+      <c r="P43" s="4" t="n">
+        <v>2366.67</v>
+      </c>
+      <c r="Q43" s="4" t="n">
+        <v>2366.67</v>
+      </c>
+      <c r="R43" s="4" t="n">
+        <v>2366.67</v>
+      </c>
+      <c r="S43" s="4" t="n">
+        <v>2366.67</v>
+      </c>
+      <c r="T43" s="4" t="n">
+        <v>28400</v>
+      </c>
       <c r="U43" s="4" t="n"/>
       <c r="V43" s="4" t="n"/>
       <c r="W43" s="4" t="n"/>
@@ -5418,12 +5468,7 @@
     </row>
     <row r="44">
       <c r="B44" t="n">
-        <v>1351</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>außerordentlicher Ertrag</t>
-        </is>
+        <v>1350</v>
       </c>
       <c r="F44" s="4" t="n"/>
       <c r="G44" s="4" t="n"/>
@@ -5463,11 +5508,11 @@
     </row>
     <row r="45">
       <c r="B45" t="n">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>außerordentlicher Aufwand</t>
+          <t>außerordentlicher Ertrag</t>
         </is>
       </c>
       <c r="F45" s="4" t="n"/>
@@ -5508,58 +5553,28 @@
     </row>
     <row r="46">
       <c r="B46" t="n">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Außerordentliches Ergebnis</t>
-        </is>
-      </c>
-      <c r="F46" s="4" t="n">
-        <v>27264</v>
-      </c>
-      <c r="G46" s="4" t="n">
-        <v>27832</v>
-      </c>
-      <c r="H46" s="4" t="n">
-        <v>2366.67</v>
-      </c>
-      <c r="I46" s="4" t="n">
-        <v>2366.67</v>
-      </c>
-      <c r="J46" s="4" t="n">
-        <v>2366.67</v>
-      </c>
-      <c r="K46" s="4" t="n">
-        <v>2366.67</v>
-      </c>
-      <c r="L46" s="4" t="n">
-        <v>2366.67</v>
-      </c>
-      <c r="M46" s="4" t="n">
-        <v>2366.67</v>
-      </c>
-      <c r="N46" s="4" t="n">
-        <v>2366.67</v>
-      </c>
-      <c r="O46" s="4" t="n">
-        <v>2366.67</v>
-      </c>
-      <c r="P46" s="4" t="n">
-        <v>2366.67</v>
-      </c>
-      <c r="Q46" s="4" t="n">
-        <v>2366.67</v>
-      </c>
-      <c r="R46" s="4" t="n">
-        <v>2366.67</v>
-      </c>
-      <c r="S46" s="4" t="n">
-        <v>2366.67</v>
-      </c>
-      <c r="T46" s="4" t="n">
-        <v>28400</v>
-      </c>
+          <t>außerordentlicher Aufwand</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="n"/>
+      <c r="G46" s="4" t="n"/>
+      <c r="H46" s="4" t="n"/>
+      <c r="I46" s="4" t="n"/>
+      <c r="J46" s="4" t="n"/>
+      <c r="K46" s="4" t="n"/>
+      <c r="L46" s="4" t="n"/>
+      <c r="M46" s="4" t="n"/>
+      <c r="N46" s="4" t="n"/>
+      <c r="O46" s="4" t="n"/>
+      <c r="P46" s="4" t="n"/>
+      <c r="Q46" s="4" t="n"/>
+      <c r="R46" s="4" t="n"/>
+      <c r="S46" s="4" t="n"/>
+      <c r="T46" s="4" t="n"/>
       <c r="U46" s="4" t="n"/>
       <c r="V46" s="4" t="n"/>
       <c r="W46" s="4" t="n"/>
@@ -5583,23 +5598,58 @@
     </row>
     <row r="47">
       <c r="B47" t="n">
-        <v>1354</v>
-      </c>
-      <c r="F47" s="4" t="n"/>
-      <c r="G47" s="4" t="n"/>
-      <c r="H47" s="4" t="n"/>
-      <c r="I47" s="4" t="n"/>
-      <c r="J47" s="4" t="n"/>
-      <c r="K47" s="4" t="n"/>
-      <c r="L47" s="4" t="n"/>
-      <c r="M47" s="4" t="n"/>
-      <c r="N47" s="4" t="n"/>
-      <c r="O47" s="4" t="n"/>
-      <c r="P47" s="4" t="n"/>
-      <c r="Q47" s="4" t="n"/>
-      <c r="R47" s="4" t="n"/>
-      <c r="S47" s="4" t="n"/>
-      <c r="T47" s="4" t="n"/>
+        <v>1353</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Außerordentliches Ergebnis</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="n">
+        <v>27264</v>
+      </c>
+      <c r="G47" s="4" t="n">
+        <v>27832</v>
+      </c>
+      <c r="H47" s="4" t="n">
+        <v>2366.67</v>
+      </c>
+      <c r="I47" s="4" t="n">
+        <v>2366.67</v>
+      </c>
+      <c r="J47" s="4" t="n">
+        <v>2366.67</v>
+      </c>
+      <c r="K47" s="4" t="n">
+        <v>2366.67</v>
+      </c>
+      <c r="L47" s="4" t="n">
+        <v>2366.67</v>
+      </c>
+      <c r="M47" s="4" t="n">
+        <v>2366.67</v>
+      </c>
+      <c r="N47" s="4" t="n">
+        <v>2366.67</v>
+      </c>
+      <c r="O47" s="4" t="n">
+        <v>2366.67</v>
+      </c>
+      <c r="P47" s="4" t="n">
+        <v>2366.67</v>
+      </c>
+      <c r="Q47" s="4" t="n">
+        <v>2366.67</v>
+      </c>
+      <c r="R47" s="4" t="n">
+        <v>2366.67</v>
+      </c>
+      <c r="S47" s="4" t="n">
+        <v>2366.67</v>
+      </c>
+      <c r="T47" s="4" t="n">
+        <v>28400</v>
+      </c>
       <c r="U47" s="4" t="n"/>
       <c r="V47" s="4" t="n"/>
       <c r="W47" s="4" t="n"/>
@@ -5623,12 +5673,7 @@
     </row>
     <row r="48">
       <c r="B48" t="n">
-        <v>1355</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Steuern Eink.u.Ertr</t>
-        </is>
+        <v>1354</v>
       </c>
       <c r="F48" s="4" t="n"/>
       <c r="G48" s="4" t="n"/>
@@ -5668,7 +5713,12 @@
     </row>
     <row r="49">
       <c r="B49" t="n">
-        <v>1360</v>
+        <v>1355</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Steuern Eink.u.Ertr</t>
+        </is>
       </c>
       <c r="F49" s="4" t="n"/>
       <c r="G49" s="4" t="n"/>
@@ -5708,58 +5758,23 @@
     </row>
     <row r="50">
       <c r="B50" t="n">
-        <v>1380</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Vorläufiges Ergebnis</t>
-        </is>
-      </c>
-      <c r="F50" s="4" t="n">
-        <v>27264</v>
-      </c>
-      <c r="G50" s="4" t="n">
-        <v>27832</v>
-      </c>
-      <c r="H50" s="4" t="n">
-        <v>2366.67</v>
-      </c>
-      <c r="I50" s="4" t="n">
-        <v>2366.67</v>
-      </c>
-      <c r="J50" s="4" t="n">
-        <v>2366.67</v>
-      </c>
-      <c r="K50" s="4" t="n">
-        <v>2366.67</v>
-      </c>
-      <c r="L50" s="4" t="n">
-        <v>2366.67</v>
-      </c>
-      <c r="M50" s="4" t="n">
-        <v>2366.67</v>
-      </c>
-      <c r="N50" s="4" t="n">
-        <v>2366.67</v>
-      </c>
-      <c r="O50" s="4" t="n">
-        <v>2366.67</v>
-      </c>
-      <c r="P50" s="4" t="n">
-        <v>2366.67</v>
-      </c>
-      <c r="Q50" s="4" t="n">
-        <v>2366.67</v>
-      </c>
-      <c r="R50" s="4" t="n">
-        <v>2366.67</v>
-      </c>
-      <c r="S50" s="4" t="n">
-        <v>2366.67</v>
-      </c>
-      <c r="T50" s="4" t="n">
-        <v>28400</v>
-      </c>
+        <v>1360</v>
+      </c>
+      <c r="F50" s="4" t="n"/>
+      <c r="G50" s="4" t="n"/>
+      <c r="H50" s="4" t="n"/>
+      <c r="I50" s="4" t="n"/>
+      <c r="J50" s="4" t="n"/>
+      <c r="K50" s="4" t="n"/>
+      <c r="L50" s="4" t="n"/>
+      <c r="M50" s="4" t="n"/>
+      <c r="N50" s="4" t="n"/>
+      <c r="O50" s="4" t="n"/>
+      <c r="P50" s="4" t="n"/>
+      <c r="Q50" s="4" t="n"/>
+      <c r="R50" s="4" t="n"/>
+      <c r="S50" s="4" t="n"/>
+      <c r="T50" s="4" t="n"/>
       <c r="U50" s="4" t="n"/>
       <c r="V50" s="4" t="n"/>
       <c r="W50" s="4" t="n"/>
@@ -5781,68 +5796,143 @@
       <c r="AM50" s="4" t="n"/>
       <c r="AN50" s="4" t="n"/>
     </row>
-    <row r="53">
-      <c r="C53" s="1" t="inlineStr">
+    <row r="51">
+      <c r="B51" t="n">
+        <v>1380</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Vorläufiges Ergebnis</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="n">
+        <v>27264</v>
+      </c>
+      <c r="G51" s="4" t="n">
+        <v>27832</v>
+      </c>
+      <c r="H51" s="4" t="n">
+        <v>2366.67</v>
+      </c>
+      <c r="I51" s="4" t="n">
+        <v>2366.67</v>
+      </c>
+      <c r="J51" s="4" t="n">
+        <v>2366.67</v>
+      </c>
+      <c r="K51" s="4" t="n">
+        <v>2366.67</v>
+      </c>
+      <c r="L51" s="4" t="n">
+        <v>2366.67</v>
+      </c>
+      <c r="M51" s="4" t="n">
+        <v>2366.67</v>
+      </c>
+      <c r="N51" s="4" t="n">
+        <v>2366.67</v>
+      </c>
+      <c r="O51" s="4" t="n">
+        <v>2366.67</v>
+      </c>
+      <c r="P51" s="4" t="n">
+        <v>2366.67</v>
+      </c>
+      <c r="Q51" s="4" t="n">
+        <v>2366.67</v>
+      </c>
+      <c r="R51" s="4" t="n">
+        <v>2366.67</v>
+      </c>
+      <c r="S51" s="4" t="n">
+        <v>2366.67</v>
+      </c>
+      <c r="T51" s="4" t="n">
+        <v>28400</v>
+      </c>
+      <c r="U51" s="4" t="n"/>
+      <c r="V51" s="4" t="n"/>
+      <c r="W51" s="4" t="n"/>
+      <c r="X51" s="4" t="n"/>
+      <c r="Y51" s="4" t="n"/>
+      <c r="Z51" s="4" t="n"/>
+      <c r="AA51" s="4" t="n"/>
+      <c r="AB51" s="4" t="n"/>
+      <c r="AC51" s="4" t="n"/>
+      <c r="AD51" s="4" t="n"/>
+      <c r="AE51" s="4" t="n"/>
+      <c r="AF51" s="4" t="n"/>
+      <c r="AG51" s="4" t="n"/>
+      <c r="AH51" s="4" t="n"/>
+      <c r="AI51" s="4" t="n"/>
+      <c r="AJ51" s="4" t="n"/>
+      <c r="AK51" s="4" t="n"/>
+      <c r="AL51" s="4" t="n"/>
+      <c r="AM51" s="4" t="n"/>
+      <c r="AN51" s="4" t="n"/>
+    </row>
+    <row r="54">
+      <c r="C54" s="1" t="inlineStr">
         <is>
           <t>Buchwert, JE</t>
-        </is>
-      </c>
-      <c r="G53" t="n">
-        <v>496000</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Wohnbau 1</t>
         </is>
       </c>
       <c r="G54" t="n">
         <v>496000</v>
       </c>
     </row>
-    <row r="56">
-      <c r="C56" s="1" t="inlineStr">
+    <row r="55">
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Wohnbau 1</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>496000</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="C57" s="1" t="inlineStr">
         <is>
           <t>Abschreibungen JW</t>
         </is>
       </c>
-      <c r="G56" t="n">
-        <v>16000</v>
-      </c>
-    </row>
-    <row r="57">
       <c r="G57" t="n">
         <v>16000</v>
       </c>
     </row>
     <row r="58">
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Wohnbau 1</t>
-        </is>
-      </c>
       <c r="G58" t="n">
         <v>16000</v>
       </c>
     </row>
-    <row r="60">
-      <c r="C60" s="1" t="inlineStr">
+    <row r="59">
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Wohnbau 1</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>16000</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="C61" s="1" t="inlineStr">
         <is>
           <t>Abschreibungen MW</t>
         </is>
       </c>
-      <c r="G60" t="n">
+      <c r="G61" t="n">
         <v>1333.333333333333</v>
       </c>
     </row>
-    <row r="61">
-      <c r="C61" t="inlineStr">
+    <row r="62">
+      <c r="C62" t="inlineStr">
         <is>
           <t>Wohnbau 1</t>
         </is>
       </c>
-      <c r="G61" t="n">
+      <c r="G62" t="n">
         <v>1333.33</v>
       </c>
     </row>
@@ -5857,7 +5947,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:AN70"/>
+  <dimension ref="B2:AN71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="3" max="3"/>
@@ -7009,11 +7099,11 @@
     </row>
     <row r="23">
       <c r="B23" t="n">
-        <v>1180</v>
+        <v>1160</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Kfz-Kosten (o. St.)</t>
+          <t>Besondere Kosten</t>
         </is>
       </c>
       <c r="F23" s="4" t="n"/>
@@ -7054,11 +7144,11 @@
     </row>
     <row r="24">
       <c r="B24" t="n">
-        <v>1200</v>
+        <v>1180</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Werbe-/Reisekosten</t>
+          <t>Kfz-Kosten (o. St.)</t>
         </is>
       </c>
       <c r="F24" s="4" t="n"/>
@@ -7099,11 +7189,11 @@
     </row>
     <row r="25">
       <c r="B25" t="n">
-        <v>1220</v>
+        <v>1200</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Kosten Warenabgabe</t>
+          <t>Werbe-/Reisekosten</t>
         </is>
       </c>
       <c r="F25" s="4" t="n"/>
@@ -7144,58 +7234,28 @@
     </row>
     <row r="26">
       <c r="B26" t="n">
-        <v>1240</v>
+        <v>1220</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Abschreibungen</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="n">
-        <v>28800</v>
-      </c>
-      <c r="G26" s="4" t="n">
-        <v>29400</v>
-      </c>
-      <c r="H26" s="4" t="n">
-        <v>2500</v>
-      </c>
-      <c r="I26" s="4" t="n">
-        <v>2500</v>
-      </c>
-      <c r="J26" s="4" t="n">
-        <v>2500</v>
-      </c>
-      <c r="K26" s="4" t="n">
-        <v>2500</v>
-      </c>
-      <c r="L26" s="4" t="n">
-        <v>2500</v>
-      </c>
-      <c r="M26" s="4" t="n">
-        <v>2500</v>
-      </c>
-      <c r="N26" s="4" t="n">
-        <v>2500</v>
-      </c>
-      <c r="O26" s="4" t="n">
-        <v>2500</v>
-      </c>
-      <c r="P26" s="4" t="n">
-        <v>2500</v>
-      </c>
-      <c r="Q26" s="4" t="n">
-        <v>2500</v>
-      </c>
-      <c r="R26" s="4" t="n">
-        <v>2500</v>
-      </c>
-      <c r="S26" s="4" t="n">
-        <v>2500</v>
-      </c>
-      <c r="T26" s="4" t="n">
-        <v>30000</v>
-      </c>
+          <t>Kosten Warenabgabe</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="n"/>
+      <c r="G26" s="4" t="n"/>
+      <c r="H26" s="4" t="n"/>
+      <c r="I26" s="4" t="n"/>
+      <c r="J26" s="4" t="n"/>
+      <c r="K26" s="4" t="n"/>
+      <c r="L26" s="4" t="n"/>
+      <c r="M26" s="4" t="n"/>
+      <c r="N26" s="4" t="n"/>
+      <c r="O26" s="4" t="n"/>
+      <c r="P26" s="4" t="n"/>
+      <c r="Q26" s="4" t="n"/>
+      <c r="R26" s="4" t="n"/>
+      <c r="S26" s="4" t="n"/>
+      <c r="T26" s="4" t="n"/>
       <c r="U26" s="4" t="n"/>
       <c r="V26" s="4" t="n"/>
       <c r="W26" s="4" t="n"/>
@@ -7219,57 +7279,57 @@
     </row>
     <row r="27">
       <c r="B27" t="n">
-        <v>1250</v>
+        <v>1240</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Reparatur/Instandh.</t>
+          <t>Abschreibungen</t>
         </is>
       </c>
       <c r="F27" s="4" t="n">
-        <v>13440</v>
+        <v>28800</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>13720</v>
+        <v>29400</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>1166.67</v>
+        <v>2500</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>1166.67</v>
+        <v>2500</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>1166.67</v>
+        <v>2500</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>1166.67</v>
+        <v>2500</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>1166.67</v>
+        <v>2500</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>1166.67</v>
+        <v>2500</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>1166.67</v>
+        <v>2500</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>1166.67</v>
+        <v>2500</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>1166.67</v>
+        <v>2500</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>1166.67</v>
+        <v>2500</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>1166.67</v>
+        <v>2500</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>1166.67</v>
+        <v>2500</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>14000</v>
+        <v>30000</v>
       </c>
       <c r="U27" s="4" t="n"/>
       <c r="V27" s="4" t="n"/>
@@ -7294,57 +7354,57 @@
     </row>
     <row r="28">
       <c r="B28" t="n">
-        <v>1260</v>
+        <v>1250</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sonstige Kosten</t>
+          <t>Reparatur/Instandh.</t>
         </is>
       </c>
       <c r="F28" s="4" t="n">
-        <v>1056</v>
+        <v>13440</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>1078</v>
+        <v>13720</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>91.67</v>
+        <v>1166.67</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>91.67</v>
+        <v>1166.67</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>91.67</v>
+        <v>1166.67</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>91.67</v>
+        <v>1166.67</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>91.67</v>
+        <v>1166.67</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>91.67</v>
+        <v>1166.67</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>91.67</v>
+        <v>1166.67</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>91.67</v>
+        <v>1166.67</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>91.67</v>
+        <v>1166.67</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>91.67</v>
+        <v>1166.67</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>91.67</v>
+        <v>1166.67</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>91.67</v>
+        <v>1166.67</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>1100</v>
+        <v>14000</v>
       </c>
       <c r="U28" s="4" t="n"/>
       <c r="V28" s="4" t="n"/>
@@ -7369,57 +7429,57 @@
     </row>
     <row r="29">
       <c r="B29" t="n">
-        <v>1280</v>
+        <v>1260</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Gesamtkosten</t>
+          <t>Sonstige Kosten</t>
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>51168</v>
+        <v>1056</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>52234</v>
+        <v>1078</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>4441.67</v>
+        <v>91.67</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>4441.67</v>
+        <v>91.67</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>4441.67</v>
+        <v>91.67</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>4441.67</v>
+        <v>91.67</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>4441.67</v>
+        <v>91.67</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>4441.67</v>
+        <v>91.67</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>4441.67</v>
+        <v>91.67</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>4441.67</v>
+        <v>91.67</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>4441.67</v>
+        <v>91.67</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>4441.67</v>
+        <v>91.67</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>4441.67</v>
+        <v>91.67</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>4441.67</v>
+        <v>91.67</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>53300</v>
+        <v>1100</v>
       </c>
       <c r="U29" s="4" t="n"/>
       <c r="V29" s="4" t="n"/>
@@ -7444,23 +7504,58 @@
     </row>
     <row r="30">
       <c r="B30" t="n">
-        <v>1290</v>
-      </c>
-      <c r="F30" s="4" t="n"/>
-      <c r="G30" s="4" t="n"/>
-      <c r="H30" s="4" t="n"/>
-      <c r="I30" s="4" t="n"/>
-      <c r="J30" s="4" t="n"/>
-      <c r="K30" s="4" t="n"/>
-      <c r="L30" s="4" t="n"/>
-      <c r="M30" s="4" t="n"/>
-      <c r="N30" s="4" t="n"/>
-      <c r="O30" s="4" t="n"/>
-      <c r="P30" s="4" t="n"/>
-      <c r="Q30" s="4" t="n"/>
-      <c r="R30" s="4" t="n"/>
-      <c r="S30" s="4" t="n"/>
-      <c r="T30" s="4" t="n"/>
+        <v>1280</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Gesamtkosten</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>51168</v>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>52234</v>
+      </c>
+      <c r="H30" s="4" t="n">
+        <v>4441.67</v>
+      </c>
+      <c r="I30" s="4" t="n">
+        <v>4441.67</v>
+      </c>
+      <c r="J30" s="4" t="n">
+        <v>4441.67</v>
+      </c>
+      <c r="K30" s="4" t="n">
+        <v>4441.67</v>
+      </c>
+      <c r="L30" s="4" t="n">
+        <v>4441.67</v>
+      </c>
+      <c r="M30" s="4" t="n">
+        <v>4441.67</v>
+      </c>
+      <c r="N30" s="4" t="n">
+        <v>4441.67</v>
+      </c>
+      <c r="O30" s="4" t="n">
+        <v>4441.67</v>
+      </c>
+      <c r="P30" s="4" t="n">
+        <v>4441.67</v>
+      </c>
+      <c r="Q30" s="4" t="n">
+        <v>4441.67</v>
+      </c>
+      <c r="R30" s="4" t="n">
+        <v>4441.67</v>
+      </c>
+      <c r="S30" s="4" t="n">
+        <v>4441.67</v>
+      </c>
+      <c r="T30" s="4" t="n">
+        <v>53300</v>
+      </c>
       <c r="U30" s="4" t="n"/>
       <c r="V30" s="4" t="n"/>
       <c r="W30" s="4" t="n"/>
@@ -7484,58 +7579,23 @@
     </row>
     <row r="31">
       <c r="B31" t="n">
-        <v>1300</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Betriebsergebnis</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="n">
-        <v>65472</v>
-      </c>
-      <c r="G31" s="4" t="n">
-        <v>66836</v>
-      </c>
-      <c r="H31" s="4" t="n">
-        <v>5683.33</v>
-      </c>
-      <c r="I31" s="4" t="n">
-        <v>5683.33</v>
-      </c>
-      <c r="J31" s="4" t="n">
-        <v>5683.33</v>
-      </c>
-      <c r="K31" s="4" t="n">
-        <v>5683.33</v>
-      </c>
-      <c r="L31" s="4" t="n">
-        <v>5683.33</v>
-      </c>
-      <c r="M31" s="4" t="n">
-        <v>5683.33</v>
-      </c>
-      <c r="N31" s="4" t="n">
-        <v>5683.33</v>
-      </c>
-      <c r="O31" s="4" t="n">
-        <v>5683.33</v>
-      </c>
-      <c r="P31" s="4" t="n">
-        <v>5683.33</v>
-      </c>
-      <c r="Q31" s="4" t="n">
-        <v>5683.33</v>
-      </c>
-      <c r="R31" s="4" t="n">
-        <v>5683.33</v>
-      </c>
-      <c r="S31" s="4" t="n">
-        <v>5683.33</v>
-      </c>
-      <c r="T31" s="4" t="n">
-        <v>68200</v>
-      </c>
+        <v>1290</v>
+      </c>
+      <c r="F31" s="4" t="n"/>
+      <c r="G31" s="4" t="n"/>
+      <c r="H31" s="4" t="n"/>
+      <c r="I31" s="4" t="n"/>
+      <c r="J31" s="4" t="n"/>
+      <c r="K31" s="4" t="n"/>
+      <c r="L31" s="4" t="n"/>
+      <c r="M31" s="4" t="n"/>
+      <c r="N31" s="4" t="n"/>
+      <c r="O31" s="4" t="n"/>
+      <c r="P31" s="4" t="n"/>
+      <c r="Q31" s="4" t="n"/>
+      <c r="R31" s="4" t="n"/>
+      <c r="S31" s="4" t="n"/>
+      <c r="T31" s="4" t="n"/>
       <c r="U31" s="4" t="n"/>
       <c r="V31" s="4" t="n"/>
       <c r="W31" s="4" t="n"/>
@@ -7559,23 +7619,58 @@
     </row>
     <row r="32">
       <c r="B32" t="n">
-        <v>1301</v>
-      </c>
-      <c r="F32" s="4" t="n"/>
-      <c r="G32" s="4" t="n"/>
-      <c r="H32" s="4" t="n"/>
-      <c r="I32" s="4" t="n"/>
-      <c r="J32" s="4" t="n"/>
-      <c r="K32" s="4" t="n"/>
-      <c r="L32" s="4" t="n"/>
-      <c r="M32" s="4" t="n"/>
-      <c r="N32" s="4" t="n"/>
-      <c r="O32" s="4" t="n"/>
-      <c r="P32" s="4" t="n"/>
-      <c r="Q32" s="4" t="n"/>
-      <c r="R32" s="4" t="n"/>
-      <c r="S32" s="4" t="n"/>
-      <c r="T32" s="4" t="n"/>
+        <v>1300</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Betriebsergebnis</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>65472</v>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>66836</v>
+      </c>
+      <c r="H32" s="4" t="n">
+        <v>5683.33</v>
+      </c>
+      <c r="I32" s="4" t="n">
+        <v>5683.33</v>
+      </c>
+      <c r="J32" s="4" t="n">
+        <v>5683.33</v>
+      </c>
+      <c r="K32" s="4" t="n">
+        <v>5683.33</v>
+      </c>
+      <c r="L32" s="4" t="n">
+        <v>5683.33</v>
+      </c>
+      <c r="M32" s="4" t="n">
+        <v>5683.33</v>
+      </c>
+      <c r="N32" s="4" t="n">
+        <v>5683.33</v>
+      </c>
+      <c r="O32" s="4" t="n">
+        <v>5683.33</v>
+      </c>
+      <c r="P32" s="4" t="n">
+        <v>5683.33</v>
+      </c>
+      <c r="Q32" s="4" t="n">
+        <v>5683.33</v>
+      </c>
+      <c r="R32" s="4" t="n">
+        <v>5683.33</v>
+      </c>
+      <c r="S32" s="4" t="n">
+        <v>5683.33</v>
+      </c>
+      <c r="T32" s="4" t="n">
+        <v>68200</v>
+      </c>
       <c r="U32" s="4" t="n"/>
       <c r="V32" s="4" t="n"/>
       <c r="W32" s="4" t="n"/>
@@ -7599,58 +7694,23 @@
     </row>
     <row r="33">
       <c r="B33" t="n">
-        <v>1310</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Zinsaufwand</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="n">
-        <v>8640</v>
-      </c>
-      <c r="G33" s="4" t="n">
-        <v>8820</v>
-      </c>
-      <c r="H33" s="4" t="n">
-        <v>750</v>
-      </c>
-      <c r="I33" s="4" t="n">
-        <v>750</v>
-      </c>
-      <c r="J33" s="4" t="n">
-        <v>750</v>
-      </c>
-      <c r="K33" s="4" t="n">
-        <v>750</v>
-      </c>
-      <c r="L33" s="4" t="n">
-        <v>750</v>
-      </c>
-      <c r="M33" s="4" t="n">
-        <v>750</v>
-      </c>
-      <c r="N33" s="4" t="n">
-        <v>750</v>
-      </c>
-      <c r="O33" s="4" t="n">
-        <v>750</v>
-      </c>
-      <c r="P33" s="4" t="n">
-        <v>750</v>
-      </c>
-      <c r="Q33" s="4" t="n">
-        <v>750</v>
-      </c>
-      <c r="R33" s="4" t="n">
-        <v>750</v>
-      </c>
-      <c r="S33" s="4" t="n">
-        <v>750</v>
-      </c>
-      <c r="T33" s="4" t="n">
-        <v>9000</v>
-      </c>
+        <v>1301</v>
+      </c>
+      <c r="F33" s="4" t="n"/>
+      <c r="G33" s="4" t="n"/>
+      <c r="H33" s="4" t="n"/>
+      <c r="I33" s="4" t="n"/>
+      <c r="J33" s="4" t="n"/>
+      <c r="K33" s="4" t="n"/>
+      <c r="L33" s="4" t="n"/>
+      <c r="M33" s="4" t="n"/>
+      <c r="N33" s="4" t="n"/>
+      <c r="O33" s="4" t="n"/>
+      <c r="P33" s="4" t="n"/>
+      <c r="Q33" s="4" t="n"/>
+      <c r="R33" s="4" t="n"/>
+      <c r="S33" s="4" t="n"/>
+      <c r="T33" s="4" t="n"/>
       <c r="U33" s="4" t="n"/>
       <c r="V33" s="4" t="n"/>
       <c r="W33" s="4" t="n"/>
@@ -7674,28 +7734,58 @@
     </row>
     <row r="34">
       <c r="B34" t="n">
-        <v>1312</v>
+        <v>1310</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sonst. neutr. Aufw</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="n"/>
-      <c r="G34" s="4" t="n"/>
-      <c r="H34" s="4" t="n"/>
-      <c r="I34" s="4" t="n"/>
-      <c r="J34" s="4" t="n"/>
-      <c r="K34" s="4" t="n"/>
-      <c r="L34" s="4" t="n"/>
-      <c r="M34" s="4" t="n"/>
-      <c r="N34" s="4" t="n"/>
-      <c r="O34" s="4" t="n"/>
-      <c r="P34" s="4" t="n"/>
-      <c r="Q34" s="4" t="n"/>
-      <c r="R34" s="4" t="n"/>
-      <c r="S34" s="4" t="n"/>
-      <c r="T34" s="4" t="n"/>
+          <t>Zinsaufwand</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>8640</v>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>8820</v>
+      </c>
+      <c r="H34" s="4" t="n">
+        <v>750</v>
+      </c>
+      <c r="I34" s="4" t="n">
+        <v>750</v>
+      </c>
+      <c r="J34" s="4" t="n">
+        <v>750</v>
+      </c>
+      <c r="K34" s="4" t="n">
+        <v>750</v>
+      </c>
+      <c r="L34" s="4" t="n">
+        <v>750</v>
+      </c>
+      <c r="M34" s="4" t="n">
+        <v>750</v>
+      </c>
+      <c r="N34" s="4" t="n">
+        <v>750</v>
+      </c>
+      <c r="O34" s="4" t="n">
+        <v>750</v>
+      </c>
+      <c r="P34" s="4" t="n">
+        <v>750</v>
+      </c>
+      <c r="Q34" s="4" t="n">
+        <v>750</v>
+      </c>
+      <c r="R34" s="4" t="n">
+        <v>750</v>
+      </c>
+      <c r="S34" s="4" t="n">
+        <v>750</v>
+      </c>
+      <c r="T34" s="4" t="n">
+        <v>9000</v>
+      </c>
       <c r="U34" s="4" t="n"/>
       <c r="V34" s="4" t="n"/>
       <c r="W34" s="4" t="n"/>
@@ -7719,58 +7809,28 @@
     </row>
     <row r="35">
       <c r="B35" t="n">
-        <v>1320</v>
+        <v>1312</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Neutraler Aufwand</t>
-        </is>
-      </c>
-      <c r="F35" s="4" t="n">
-        <v>8640</v>
-      </c>
-      <c r="G35" s="4" t="n">
-        <v>8820</v>
-      </c>
-      <c r="H35" s="4" t="n">
-        <v>750</v>
-      </c>
-      <c r="I35" s="4" t="n">
-        <v>750</v>
-      </c>
-      <c r="J35" s="4" t="n">
-        <v>750</v>
-      </c>
-      <c r="K35" s="4" t="n">
-        <v>750</v>
-      </c>
-      <c r="L35" s="4" t="n">
-        <v>750</v>
-      </c>
-      <c r="M35" s="4" t="n">
-        <v>750</v>
-      </c>
-      <c r="N35" s="4" t="n">
-        <v>750</v>
-      </c>
-      <c r="O35" s="4" t="n">
-        <v>750</v>
-      </c>
-      <c r="P35" s="4" t="n">
-        <v>750</v>
-      </c>
-      <c r="Q35" s="4" t="n">
-        <v>750</v>
-      </c>
-      <c r="R35" s="4" t="n">
-        <v>750</v>
-      </c>
-      <c r="S35" s="4" t="n">
-        <v>750</v>
-      </c>
-      <c r="T35" s="4" t="n">
-        <v>9000</v>
-      </c>
+          <t>Sonst. neutr. Aufw</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="n"/>
+      <c r="G35" s="4" t="n"/>
+      <c r="H35" s="4" t="n"/>
+      <c r="I35" s="4" t="n"/>
+      <c r="J35" s="4" t="n"/>
+      <c r="K35" s="4" t="n"/>
+      <c r="L35" s="4" t="n"/>
+      <c r="M35" s="4" t="n"/>
+      <c r="N35" s="4" t="n"/>
+      <c r="O35" s="4" t="n"/>
+      <c r="P35" s="4" t="n"/>
+      <c r="Q35" s="4" t="n"/>
+      <c r="R35" s="4" t="n"/>
+      <c r="S35" s="4" t="n"/>
+      <c r="T35" s="4" t="n"/>
       <c r="U35" s="4" t="n"/>
       <c r="V35" s="4" t="n"/>
       <c r="W35" s="4" t="n"/>
@@ -7794,23 +7854,58 @@
     </row>
     <row r="36">
       <c r="B36" t="n">
-        <v>1321</v>
-      </c>
-      <c r="F36" s="4" t="n"/>
-      <c r="G36" s="4" t="n"/>
-      <c r="H36" s="4" t="n"/>
-      <c r="I36" s="4" t="n"/>
-      <c r="J36" s="4" t="n"/>
-      <c r="K36" s="4" t="n"/>
-      <c r="L36" s="4" t="n"/>
-      <c r="M36" s="4" t="n"/>
-      <c r="N36" s="4" t="n"/>
-      <c r="O36" s="4" t="n"/>
-      <c r="P36" s="4" t="n"/>
-      <c r="Q36" s="4" t="n"/>
-      <c r="R36" s="4" t="n"/>
-      <c r="S36" s="4" t="n"/>
-      <c r="T36" s="4" t="n"/>
+        <v>1320</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Neutraler Aufwand</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>8640</v>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>8820</v>
+      </c>
+      <c r="H36" s="4" t="n">
+        <v>750</v>
+      </c>
+      <c r="I36" s="4" t="n">
+        <v>750</v>
+      </c>
+      <c r="J36" s="4" t="n">
+        <v>750</v>
+      </c>
+      <c r="K36" s="4" t="n">
+        <v>750</v>
+      </c>
+      <c r="L36" s="4" t="n">
+        <v>750</v>
+      </c>
+      <c r="M36" s="4" t="n">
+        <v>750</v>
+      </c>
+      <c r="N36" s="4" t="n">
+        <v>750</v>
+      </c>
+      <c r="O36" s="4" t="n">
+        <v>750</v>
+      </c>
+      <c r="P36" s="4" t="n">
+        <v>750</v>
+      </c>
+      <c r="Q36" s="4" t="n">
+        <v>750</v>
+      </c>
+      <c r="R36" s="4" t="n">
+        <v>750</v>
+      </c>
+      <c r="S36" s="4" t="n">
+        <v>750</v>
+      </c>
+      <c r="T36" s="4" t="n">
+        <v>9000</v>
+      </c>
       <c r="U36" s="4" t="n"/>
       <c r="V36" s="4" t="n"/>
       <c r="W36" s="4" t="n"/>
@@ -7834,58 +7929,23 @@
     </row>
     <row r="37">
       <c r="B37" t="n">
-        <v>1322</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Zinserträge</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="n">
-        <v>288</v>
-      </c>
-      <c r="G37" s="4" t="n">
-        <v>294</v>
-      </c>
-      <c r="H37" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="I37" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="J37" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="K37" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="L37" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="M37" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="N37" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="O37" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="P37" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q37" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="R37" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="S37" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="T37" s="4" t="n">
-        <v>300</v>
-      </c>
+        <v>1321</v>
+      </c>
+      <c r="F37" s="4" t="n"/>
+      <c r="G37" s="4" t="n"/>
+      <c r="H37" s="4" t="n"/>
+      <c r="I37" s="4" t="n"/>
+      <c r="J37" s="4" t="n"/>
+      <c r="K37" s="4" t="n"/>
+      <c r="L37" s="4" t="n"/>
+      <c r="M37" s="4" t="n"/>
+      <c r="N37" s="4" t="n"/>
+      <c r="O37" s="4" t="n"/>
+      <c r="P37" s="4" t="n"/>
+      <c r="Q37" s="4" t="n"/>
+      <c r="R37" s="4" t="n"/>
+      <c r="S37" s="4" t="n"/>
+      <c r="T37" s="4" t="n"/>
       <c r="U37" s="4" t="n"/>
       <c r="V37" s="4" t="n"/>
       <c r="W37" s="4" t="n"/>
@@ -7909,28 +7969,58 @@
     </row>
     <row r="38">
       <c r="B38" t="n">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sonst. neutr. Ertr</t>
-        </is>
-      </c>
-      <c r="F38" s="4" t="n"/>
-      <c r="G38" s="4" t="n"/>
-      <c r="H38" s="4" t="n"/>
-      <c r="I38" s="4" t="n"/>
-      <c r="J38" s="4" t="n"/>
-      <c r="K38" s="4" t="n"/>
-      <c r="L38" s="4" t="n"/>
-      <c r="M38" s="4" t="n"/>
-      <c r="N38" s="4" t="n"/>
-      <c r="O38" s="4" t="n"/>
-      <c r="P38" s="4" t="n"/>
-      <c r="Q38" s="4" t="n"/>
-      <c r="R38" s="4" t="n"/>
-      <c r="S38" s="4" t="n"/>
-      <c r="T38" s="4" t="n"/>
+          <t>Zinserträge</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>288</v>
+      </c>
+      <c r="G38" s="4" t="n">
+        <v>294</v>
+      </c>
+      <c r="H38" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="I38" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="J38" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="K38" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="L38" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="M38" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="N38" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="O38" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="P38" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q38" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="R38" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="S38" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T38" s="4" t="n">
+        <v>300</v>
+      </c>
       <c r="U38" s="4" t="n"/>
       <c r="V38" s="4" t="n"/>
       <c r="W38" s="4" t="n"/>
@@ -7954,58 +8044,28 @@
     </row>
     <row r="39">
       <c r="B39" t="n">
-        <v>1330</v>
+        <v>1323</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Neutraler Ertrag</t>
-        </is>
-      </c>
-      <c r="F39" s="4" t="n">
-        <v>288</v>
-      </c>
-      <c r="G39" s="4" t="n">
-        <v>294</v>
-      </c>
-      <c r="H39" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="I39" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="J39" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="K39" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="L39" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="M39" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="N39" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="O39" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="P39" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q39" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="R39" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="S39" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="T39" s="4" t="n">
-        <v>300</v>
-      </c>
+          <t>Sonst. neutr. Ertr</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="n"/>
+      <c r="G39" s="4" t="n"/>
+      <c r="H39" s="4" t="n"/>
+      <c r="I39" s="4" t="n"/>
+      <c r="J39" s="4" t="n"/>
+      <c r="K39" s="4" t="n"/>
+      <c r="L39" s="4" t="n"/>
+      <c r="M39" s="4" t="n"/>
+      <c r="N39" s="4" t="n"/>
+      <c r="O39" s="4" t="n"/>
+      <c r="P39" s="4" t="n"/>
+      <c r="Q39" s="4" t="n"/>
+      <c r="R39" s="4" t="n"/>
+      <c r="S39" s="4" t="n"/>
+      <c r="T39" s="4" t="n"/>
       <c r="U39" s="4" t="n"/>
       <c r="V39" s="4" t="n"/>
       <c r="W39" s="4" t="n"/>
@@ -8029,23 +8089,58 @@
     </row>
     <row r="40">
       <c r="B40" t="n">
-        <v>1331</v>
-      </c>
-      <c r="F40" s="4" t="n"/>
-      <c r="G40" s="4" t="n"/>
-      <c r="H40" s="4" t="n"/>
-      <c r="I40" s="4" t="n"/>
-      <c r="J40" s="4" t="n"/>
-      <c r="K40" s="4" t="n"/>
-      <c r="L40" s="4" t="n"/>
-      <c r="M40" s="4" t="n"/>
-      <c r="N40" s="4" t="n"/>
-      <c r="O40" s="4" t="n"/>
-      <c r="P40" s="4" t="n"/>
-      <c r="Q40" s="4" t="n"/>
-      <c r="R40" s="4" t="n"/>
-      <c r="S40" s="4" t="n"/>
-      <c r="T40" s="4" t="n"/>
+        <v>1330</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Neutraler Ertrag</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="n">
+        <v>288</v>
+      </c>
+      <c r="G40" s="4" t="n">
+        <v>294</v>
+      </c>
+      <c r="H40" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="I40" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="J40" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="K40" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="L40" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="M40" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="N40" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="O40" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="P40" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q40" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="R40" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="S40" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T40" s="4" t="n">
+        <v>300</v>
+      </c>
       <c r="U40" s="4" t="n"/>
       <c r="V40" s="4" t="n"/>
       <c r="W40" s="4" t="n"/>
@@ -8069,7 +8164,7 @@
     </row>
     <row r="41">
       <c r="B41" t="n">
-        <v>1342</v>
+        <v>1331</v>
       </c>
       <c r="F41" s="4" t="n"/>
       <c r="G41" s="4" t="n"/>
@@ -8109,58 +8204,23 @@
     </row>
     <row r="42">
       <c r="B42" t="n">
-        <v>1345</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ergebnis vor Steuern</t>
-        </is>
-      </c>
-      <c r="F42" s="4" t="n">
-        <v>57120</v>
-      </c>
-      <c r="G42" s="4" t="n">
-        <v>58310</v>
-      </c>
-      <c r="H42" s="4" t="n">
-        <v>4958.33</v>
-      </c>
-      <c r="I42" s="4" t="n">
-        <v>4958.33</v>
-      </c>
-      <c r="J42" s="4" t="n">
-        <v>4958.33</v>
-      </c>
-      <c r="K42" s="4" t="n">
-        <v>4958.33</v>
-      </c>
-      <c r="L42" s="4" t="n">
-        <v>4958.33</v>
-      </c>
-      <c r="M42" s="4" t="n">
-        <v>4958.33</v>
-      </c>
-      <c r="N42" s="4" t="n">
-        <v>4958.33</v>
-      </c>
-      <c r="O42" s="4" t="n">
-        <v>4958.33</v>
-      </c>
-      <c r="P42" s="4" t="n">
-        <v>4958.33</v>
-      </c>
-      <c r="Q42" s="4" t="n">
-        <v>4958.33</v>
-      </c>
-      <c r="R42" s="4" t="n">
-        <v>4958.33</v>
-      </c>
-      <c r="S42" s="4" t="n">
-        <v>4958.33</v>
-      </c>
-      <c r="T42" s="4" t="n">
-        <v>59500</v>
-      </c>
+        <v>1342</v>
+      </c>
+      <c r="F42" s="4" t="n"/>
+      <c r="G42" s="4" t="n"/>
+      <c r="H42" s="4" t="n"/>
+      <c r="I42" s="4" t="n"/>
+      <c r="J42" s="4" t="n"/>
+      <c r="K42" s="4" t="n"/>
+      <c r="L42" s="4" t="n"/>
+      <c r="M42" s="4" t="n"/>
+      <c r="N42" s="4" t="n"/>
+      <c r="O42" s="4" t="n"/>
+      <c r="P42" s="4" t="n"/>
+      <c r="Q42" s="4" t="n"/>
+      <c r="R42" s="4" t="n"/>
+      <c r="S42" s="4" t="n"/>
+      <c r="T42" s="4" t="n"/>
       <c r="U42" s="4" t="n"/>
       <c r="V42" s="4" t="n"/>
       <c r="W42" s="4" t="n"/>
@@ -8184,23 +8244,58 @@
     </row>
     <row r="43">
       <c r="B43" t="n">
-        <v>1350</v>
-      </c>
-      <c r="F43" s="4" t="n"/>
-      <c r="G43" s="4" t="n"/>
-      <c r="H43" s="4" t="n"/>
-      <c r="I43" s="4" t="n"/>
-      <c r="J43" s="4" t="n"/>
-      <c r="K43" s="4" t="n"/>
-      <c r="L43" s="4" t="n"/>
-      <c r="M43" s="4" t="n"/>
-      <c r="N43" s="4" t="n"/>
-      <c r="O43" s="4" t="n"/>
-      <c r="P43" s="4" t="n"/>
-      <c r="Q43" s="4" t="n"/>
-      <c r="R43" s="4" t="n"/>
-      <c r="S43" s="4" t="n"/>
-      <c r="T43" s="4" t="n"/>
+        <v>1345</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ergebnis vor Steuern</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="n">
+        <v>57120</v>
+      </c>
+      <c r="G43" s="4" t="n">
+        <v>58310</v>
+      </c>
+      <c r="H43" s="4" t="n">
+        <v>4958.33</v>
+      </c>
+      <c r="I43" s="4" t="n">
+        <v>4958.33</v>
+      </c>
+      <c r="J43" s="4" t="n">
+        <v>4958.33</v>
+      </c>
+      <c r="K43" s="4" t="n">
+        <v>4958.33</v>
+      </c>
+      <c r="L43" s="4" t="n">
+        <v>4958.33</v>
+      </c>
+      <c r="M43" s="4" t="n">
+        <v>4958.33</v>
+      </c>
+      <c r="N43" s="4" t="n">
+        <v>4958.33</v>
+      </c>
+      <c r="O43" s="4" t="n">
+        <v>4958.33</v>
+      </c>
+      <c r="P43" s="4" t="n">
+        <v>4958.33</v>
+      </c>
+      <c r="Q43" s="4" t="n">
+        <v>4958.33</v>
+      </c>
+      <c r="R43" s="4" t="n">
+        <v>4958.33</v>
+      </c>
+      <c r="S43" s="4" t="n">
+        <v>4958.33</v>
+      </c>
+      <c r="T43" s="4" t="n">
+        <v>59500</v>
+      </c>
       <c r="U43" s="4" t="n"/>
       <c r="V43" s="4" t="n"/>
       <c r="W43" s="4" t="n"/>
@@ -8224,12 +8319,7 @@
     </row>
     <row r="44">
       <c r="B44" t="n">
-        <v>1351</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>außerordentlicher Ertrag</t>
-        </is>
+        <v>1350</v>
       </c>
       <c r="F44" s="4" t="n"/>
       <c r="G44" s="4" t="n"/>
@@ -8269,11 +8359,11 @@
     </row>
     <row r="45">
       <c r="B45" t="n">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>außerordentlicher Aufwand</t>
+          <t>außerordentlicher Ertrag</t>
         </is>
       </c>
       <c r="F45" s="4" t="n"/>
@@ -8314,58 +8404,28 @@
     </row>
     <row r="46">
       <c r="B46" t="n">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Außerordentliches Ergebnis</t>
-        </is>
-      </c>
-      <c r="F46" s="4" t="n">
-        <v>57120</v>
-      </c>
-      <c r="G46" s="4" t="n">
-        <v>58310</v>
-      </c>
-      <c r="H46" s="4" t="n">
-        <v>4958.33</v>
-      </c>
-      <c r="I46" s="4" t="n">
-        <v>4958.33</v>
-      </c>
-      <c r="J46" s="4" t="n">
-        <v>4958.33</v>
-      </c>
-      <c r="K46" s="4" t="n">
-        <v>4958.33</v>
-      </c>
-      <c r="L46" s="4" t="n">
-        <v>4958.33</v>
-      </c>
-      <c r="M46" s="4" t="n">
-        <v>4958.33</v>
-      </c>
-      <c r="N46" s="4" t="n">
-        <v>4958.33</v>
-      </c>
-      <c r="O46" s="4" t="n">
-        <v>4958.33</v>
-      </c>
-      <c r="P46" s="4" t="n">
-        <v>4958.33</v>
-      </c>
-      <c r="Q46" s="4" t="n">
-        <v>4958.33</v>
-      </c>
-      <c r="R46" s="4" t="n">
-        <v>4958.33</v>
-      </c>
-      <c r="S46" s="4" t="n">
-        <v>4958.33</v>
-      </c>
-      <c r="T46" s="4" t="n">
-        <v>59500</v>
-      </c>
+          <t>außerordentlicher Aufwand</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="n"/>
+      <c r="G46" s="4" t="n"/>
+      <c r="H46" s="4" t="n"/>
+      <c r="I46" s="4" t="n"/>
+      <c r="J46" s="4" t="n"/>
+      <c r="K46" s="4" t="n"/>
+      <c r="L46" s="4" t="n"/>
+      <c r="M46" s="4" t="n"/>
+      <c r="N46" s="4" t="n"/>
+      <c r="O46" s="4" t="n"/>
+      <c r="P46" s="4" t="n"/>
+      <c r="Q46" s="4" t="n"/>
+      <c r="R46" s="4" t="n"/>
+      <c r="S46" s="4" t="n"/>
+      <c r="T46" s="4" t="n"/>
       <c r="U46" s="4" t="n"/>
       <c r="V46" s="4" t="n"/>
       <c r="W46" s="4" t="n"/>
@@ -8389,23 +8449,58 @@
     </row>
     <row r="47">
       <c r="B47" t="n">
-        <v>1354</v>
-      </c>
-      <c r="F47" s="4" t="n"/>
-      <c r="G47" s="4" t="n"/>
-      <c r="H47" s="4" t="n"/>
-      <c r="I47" s="4" t="n"/>
-      <c r="J47" s="4" t="n"/>
-      <c r="K47" s="4" t="n"/>
-      <c r="L47" s="4" t="n"/>
-      <c r="M47" s="4" t="n"/>
-      <c r="N47" s="4" t="n"/>
-      <c r="O47" s="4" t="n"/>
-      <c r="P47" s="4" t="n"/>
-      <c r="Q47" s="4" t="n"/>
-      <c r="R47" s="4" t="n"/>
-      <c r="S47" s="4" t="n"/>
-      <c r="T47" s="4" t="n"/>
+        <v>1353</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Außerordentliches Ergebnis</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="n">
+        <v>57120</v>
+      </c>
+      <c r="G47" s="4" t="n">
+        <v>58310</v>
+      </c>
+      <c r="H47" s="4" t="n">
+        <v>4958.33</v>
+      </c>
+      <c r="I47" s="4" t="n">
+        <v>4958.33</v>
+      </c>
+      <c r="J47" s="4" t="n">
+        <v>4958.33</v>
+      </c>
+      <c r="K47" s="4" t="n">
+        <v>4958.33</v>
+      </c>
+      <c r="L47" s="4" t="n">
+        <v>4958.33</v>
+      </c>
+      <c r="M47" s="4" t="n">
+        <v>4958.33</v>
+      </c>
+      <c r="N47" s="4" t="n">
+        <v>4958.33</v>
+      </c>
+      <c r="O47" s="4" t="n">
+        <v>4958.33</v>
+      </c>
+      <c r="P47" s="4" t="n">
+        <v>4958.33</v>
+      </c>
+      <c r="Q47" s="4" t="n">
+        <v>4958.33</v>
+      </c>
+      <c r="R47" s="4" t="n">
+        <v>4958.33</v>
+      </c>
+      <c r="S47" s="4" t="n">
+        <v>4958.33</v>
+      </c>
+      <c r="T47" s="4" t="n">
+        <v>59500</v>
+      </c>
       <c r="U47" s="4" t="n"/>
       <c r="V47" s="4" t="n"/>
       <c r="W47" s="4" t="n"/>
@@ -8429,12 +8524,7 @@
     </row>
     <row r="48">
       <c r="B48" t="n">
-        <v>1355</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Steuern Eink.u.Ertr</t>
-        </is>
+        <v>1354</v>
       </c>
       <c r="F48" s="4" t="n"/>
       <c r="G48" s="4" t="n"/>
@@ -8474,7 +8564,12 @@
     </row>
     <row r="49">
       <c r="B49" t="n">
-        <v>1360</v>
+        <v>1355</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Steuern Eink.u.Ertr</t>
+        </is>
       </c>
       <c r="F49" s="4" t="n"/>
       <c r="G49" s="4" t="n"/>
@@ -8514,58 +8609,23 @@
     </row>
     <row r="50">
       <c r="B50" t="n">
-        <v>1380</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Vorläufiges Ergebnis</t>
-        </is>
-      </c>
-      <c r="F50" s="4" t="n">
-        <v>57120</v>
-      </c>
-      <c r="G50" s="4" t="n">
-        <v>58310</v>
-      </c>
-      <c r="H50" s="4" t="n">
-        <v>4958.33</v>
-      </c>
-      <c r="I50" s="4" t="n">
-        <v>4958.33</v>
-      </c>
-      <c r="J50" s="4" t="n">
-        <v>4958.33</v>
-      </c>
-      <c r="K50" s="4" t="n">
-        <v>4958.33</v>
-      </c>
-      <c r="L50" s="4" t="n">
-        <v>4958.33</v>
-      </c>
-      <c r="M50" s="4" t="n">
-        <v>4958.33</v>
-      </c>
-      <c r="N50" s="4" t="n">
-        <v>4958.33</v>
-      </c>
-      <c r="O50" s="4" t="n">
-        <v>4958.33</v>
-      </c>
-      <c r="P50" s="4" t="n">
-        <v>4958.33</v>
-      </c>
-      <c r="Q50" s="4" t="n">
-        <v>4958.33</v>
-      </c>
-      <c r="R50" s="4" t="n">
-        <v>4958.33</v>
-      </c>
-      <c r="S50" s="4" t="n">
-        <v>4958.33</v>
-      </c>
-      <c r="T50" s="4" t="n">
-        <v>59500</v>
-      </c>
+        <v>1360</v>
+      </c>
+      <c r="F50" s="4" t="n"/>
+      <c r="G50" s="4" t="n"/>
+      <c r="H50" s="4" t="n"/>
+      <c r="I50" s="4" t="n"/>
+      <c r="J50" s="4" t="n"/>
+      <c r="K50" s="4" t="n"/>
+      <c r="L50" s="4" t="n"/>
+      <c r="M50" s="4" t="n"/>
+      <c r="N50" s="4" t="n"/>
+      <c r="O50" s="4" t="n"/>
+      <c r="P50" s="4" t="n"/>
+      <c r="Q50" s="4" t="n"/>
+      <c r="R50" s="4" t="n"/>
+      <c r="S50" s="4" t="n"/>
+      <c r="T50" s="4" t="n"/>
       <c r="U50" s="4" t="n"/>
       <c r="V50" s="4" t="n"/>
       <c r="W50" s="4" t="n"/>
@@ -8587,155 +8647,230 @@
       <c r="AM50" s="4" t="n"/>
       <c r="AN50" s="4" t="n"/>
     </row>
-    <row r="53">
-      <c r="C53" s="1" t="inlineStr">
+    <row r="51">
+      <c r="B51" t="n">
+        <v>1380</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Vorläufiges Ergebnis</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="n">
+        <v>57120</v>
+      </c>
+      <c r="G51" s="4" t="n">
+        <v>58310</v>
+      </c>
+      <c r="H51" s="4" t="n">
+        <v>4958.33</v>
+      </c>
+      <c r="I51" s="4" t="n">
+        <v>4958.33</v>
+      </c>
+      <c r="J51" s="4" t="n">
+        <v>4958.33</v>
+      </c>
+      <c r="K51" s="4" t="n">
+        <v>4958.33</v>
+      </c>
+      <c r="L51" s="4" t="n">
+        <v>4958.33</v>
+      </c>
+      <c r="M51" s="4" t="n">
+        <v>4958.33</v>
+      </c>
+      <c r="N51" s="4" t="n">
+        <v>4958.33</v>
+      </c>
+      <c r="O51" s="4" t="n">
+        <v>4958.33</v>
+      </c>
+      <c r="P51" s="4" t="n">
+        <v>4958.33</v>
+      </c>
+      <c r="Q51" s="4" t="n">
+        <v>4958.33</v>
+      </c>
+      <c r="R51" s="4" t="n">
+        <v>4958.33</v>
+      </c>
+      <c r="S51" s="4" t="n">
+        <v>4958.33</v>
+      </c>
+      <c r="T51" s="4" t="n">
+        <v>59500</v>
+      </c>
+      <c r="U51" s="4" t="n"/>
+      <c r="V51" s="4" t="n"/>
+      <c r="W51" s="4" t="n"/>
+      <c r="X51" s="4" t="n"/>
+      <c r="Y51" s="4" t="n"/>
+      <c r="Z51" s="4" t="n"/>
+      <c r="AA51" s="4" t="n"/>
+      <c r="AB51" s="4" t="n"/>
+      <c r="AC51" s="4" t="n"/>
+      <c r="AD51" s="4" t="n"/>
+      <c r="AE51" s="4" t="n"/>
+      <c r="AF51" s="4" t="n"/>
+      <c r="AG51" s="4" t="n"/>
+      <c r="AH51" s="4" t="n"/>
+      <c r="AI51" s="4" t="n"/>
+      <c r="AJ51" s="4" t="n"/>
+      <c r="AK51" s="4" t="n"/>
+      <c r="AL51" s="4" t="n"/>
+      <c r="AM51" s="4" t="n"/>
+      <c r="AN51" s="4" t="n"/>
+    </row>
+    <row r="54">
+      <c r="C54" s="1" t="inlineStr">
         <is>
           <t>Buchwert, JE</t>
         </is>
       </c>
-      <c r="G53" t="n">
+      <c r="G54" t="n">
         <v>941000</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Wohnbau 7</t>
-        </is>
-      </c>
-      <c r="G54" t="n">
-        <v>876000</v>
       </c>
     </row>
     <row r="55">
       <c r="C55" t="inlineStr">
         <is>
-          <t>Außenanlagen 7</t>
+          <t>Wohnbau 7</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>15000</v>
+        <v>876000</v>
       </c>
     </row>
     <row r="56">
       <c r="C56" t="inlineStr">
         <is>
-          <t>Anbau im Bau</t>
+          <t>Außenanlagen 7</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>50000</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="57">
       <c r="C57" t="inlineStr">
         <is>
+          <t>Anbau im Bau</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="C58" t="inlineStr">
+        <is>
           <t>sonstige</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="C59" s="1" t="inlineStr">
+    <row r="60">
+      <c r="C60" s="1" t="inlineStr">
         <is>
           <t>Abschreibungen JW</t>
         </is>
       </c>
-      <c r="G59" t="n">
-        <v>30000</v>
-      </c>
-    </row>
-    <row r="60">
       <c r="G60" t="n">
         <v>30000</v>
       </c>
     </row>
     <row r="61">
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Wohnbau</t>
-        </is>
-      </c>
       <c r="G61" t="n">
-        <v>24000</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="62">
       <c r="C62" t="inlineStr">
         <is>
-          <t>Außenanlagen</t>
+          <t>Wohnbau</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>6000</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="63">
       <c r="C63" t="inlineStr">
         <is>
-          <t>Anbau im Bau</t>
+          <t>Außenanlagen</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="64">
       <c r="C64" t="inlineStr">
         <is>
-          <t>sonstige</t>
+          <t>Anbau im Bau</t>
         </is>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="66">
-      <c r="C66" s="1" t="inlineStr">
+    <row r="65">
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>sonstige</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="C67" s="1" t="inlineStr">
         <is>
           <t>Abschreibungen MW</t>
         </is>
       </c>
-      <c r="G66" t="n">
+      <c r="G67" t="n">
         <v>2500</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Wohnbau</t>
-        </is>
-      </c>
-      <c r="G67" t="n">
-        <v>2000</v>
       </c>
     </row>
     <row r="68">
       <c r="C68" t="inlineStr">
         <is>
-          <t>Außenanlagen</t>
+          <t>Wohnbau</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>500</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="69">
       <c r="C69" t="inlineStr">
         <is>
-          <t>Anbau im Bau</t>
+          <t>Außenanlagen</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="70">
       <c r="C70" t="inlineStr">
         <is>
+          <t>Anbau im Bau</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="C71" t="inlineStr">
+        <is>
           <t>sonstige</t>
         </is>
       </c>
-      <c r="G70" t="n">
+      <c r="G71" t="n">
         <v>0</v>
       </c>
     </row>

--- a/vorlagen/Kostenstellen_BWA_Vorlage.xlsx
+++ b/vorlagen/Kostenstellen_BWA_Vorlage.xlsx
@@ -64,7 +64,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
